--- a/research/traditional_assets/database/data/canada/canada_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_heathcare_information_and_technology.xlsx
@@ -2727,7 +2727,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2864,22 +2864,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09663661468084669</v>
+        <v>0.09641360265194245</v>
       </c>
       <c r="C2">
-        <v>410.0828673880168</v>
+        <v>407.5224094136575</v>
       </c>
       <c r="D2">
-        <v>349.7828673880168</v>
+        <v>351.3240694136575</v>
       </c>
       <c r="E2">
-        <v>-0.266</v>
+        <v>3.83566</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.10166</v>
       </c>
       <c r="G2">
         <v>60.3</v>
@@ -2900,28 +2900,28 @@
         <v>5.02</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.206313498</v>
       </c>
       <c r="N2">
-        <v>5.02</v>
+        <v>4.813686502</v>
       </c>
       <c r="O2">
-        <v>1.3303</v>
+        <v>1.27562692303</v>
       </c>
       <c r="P2">
-        <v>3.6897</v>
+        <v>3.53805957897</v>
       </c>
       <c r="Q2">
-        <v>7.5697</v>
+        <v>7.41805957897</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09663661468084669</v>
+        <v>0.0970140380322651</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.18277224092991</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>24.33190289856847</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2946,22 +2946,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09641360265194245</v>
+        <v>0.09621264062303821</v>
       </c>
       <c r="C3">
-        <v>407.5224094136575</v>
+        <v>404.8212473229061</v>
       </c>
       <c r="D3">
-        <v>351.3240694136575</v>
+        <v>352.7245673229061</v>
       </c>
       <c r="E3">
-        <v>3.83566</v>
+        <v>7.93732</v>
       </c>
       <c r="F3">
-        <v>4.10166</v>
+        <v>8.20332</v>
       </c>
       <c r="G3">
         <v>60.3</v>
@@ -2982,45 +2982,45 @@
         <v>5.02</v>
       </c>
       <c r="M3">
-        <v>0.206313498</v>
+        <v>0.424931976</v>
       </c>
       <c r="N3">
-        <v>4.813686502</v>
+        <v>4.595068024000001</v>
       </c>
       <c r="O3">
-        <v>1.27562692303</v>
+        <v>1.21769302636</v>
       </c>
       <c r="P3">
-        <v>3.53805957897</v>
+        <v>3.37737499764</v>
       </c>
       <c r="Q3">
-        <v>7.41805957897</v>
+        <v>7.25737499764</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0970140380322651</v>
+        <v>0.09739916390105939</v>
       </c>
       <c r="T3">
-        <v>1.18277224092991</v>
+        <v>1.191666602795829</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.265</v>
       </c>
       <c r="W3">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>24.33190289856847</v>
+        <v>11.8136555578957</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3028,22 +3028,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09621264062303821</v>
+        <v>0.09603813859413397</v>
       </c>
       <c r="C4">
-        <v>404.8212473229061</v>
+        <v>401.9447750859217</v>
       </c>
       <c r="D4">
-        <v>352.7245673229061</v>
+        <v>353.9497550859217</v>
       </c>
       <c r="E4">
-        <v>7.93732</v>
+        <v>12.03898</v>
       </c>
       <c r="F4">
-        <v>8.20332</v>
+        <v>12.30498</v>
       </c>
       <c r="G4">
         <v>60.3</v>
@@ -3064,45 +3064,45 @@
         <v>5.02</v>
       </c>
       <c r="M4">
-        <v>0.424931976</v>
+        <v>0.65831643</v>
       </c>
       <c r="N4">
-        <v>4.595068024000001</v>
+        <v>4.36168357</v>
       </c>
       <c r="O4">
-        <v>1.21769302636</v>
+        <v>1.15584614605</v>
       </c>
       <c r="P4">
-        <v>3.37737499764</v>
+        <v>3.20583742395</v>
       </c>
       <c r="Q4">
-        <v>7.25737499764</v>
+        <v>7.08583742395</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09739916390105939</v>
+        <v>0.09779223050941646</v>
       </c>
       <c r="T4">
-        <v>1.191666602795829</v>
+        <v>1.2007443535662</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.265</v>
       </c>
       <c r="W4">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>11.8136555578957</v>
+        <v>7.62551224796258</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3110,22 +3110,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09603813859413397</v>
+        <v>0.09589156656522971</v>
       </c>
       <c r="C5">
-        <v>401.9447750859217</v>
+        <v>398.8788010764078</v>
       </c>
       <c r="D5">
-        <v>353.9497550859217</v>
+        <v>354.9854410764078</v>
       </c>
       <c r="E5">
-        <v>12.03898</v>
+        <v>16.14064</v>
       </c>
       <c r="F5">
-        <v>12.30498</v>
+        <v>16.40664</v>
       </c>
       <c r="G5">
         <v>60.3</v>
@@ -3146,45 +3146,45 @@
         <v>5.02</v>
       </c>
       <c r="M5">
-        <v>0.65831643</v>
+        <v>0.907287192</v>
       </c>
       <c r="N5">
-        <v>4.36168357</v>
+        <v>4.112712808</v>
       </c>
       <c r="O5">
-        <v>1.15584614605</v>
+        <v>1.08986889412</v>
       </c>
       <c r="P5">
-        <v>3.20583742395</v>
+        <v>3.02284391388</v>
       </c>
       <c r="Q5">
-        <v>7.08583742395</v>
+        <v>6.90284391388</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09779223050941646</v>
+        <v>0.09819348600544761</v>
       </c>
       <c r="T5">
-        <v>1.2007443535662</v>
+        <v>1.210011224144287</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.265</v>
       </c>
       <c r="W5">
-        <v>0.0393225</v>
+        <v>0.0406455</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>7.62551224796258</v>
+        <v>5.532977919520769</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -3192,22 +3192,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09589156656522971</v>
+        <v>0.09579717953632548</v>
       </c>
       <c r="C6">
-        <v>398.8788010764078</v>
+        <v>395.4472993012956</v>
       </c>
       <c r="D6">
-        <v>354.9854410764078</v>
+        <v>355.6555993012956</v>
       </c>
       <c r="E6">
-        <v>16.14064</v>
+        <v>20.2423</v>
       </c>
       <c r="F6">
-        <v>16.40664</v>
+        <v>20.5083</v>
       </c>
       <c r="G6">
         <v>60.3</v>
@@ -3228,45 +3228,45 @@
         <v>5.02</v>
       </c>
       <c r="M6">
-        <v>0.907287192</v>
+        <v>1.18537974</v>
       </c>
       <c r="N6">
-        <v>4.112712808</v>
+        <v>3.83462026</v>
       </c>
       <c r="O6">
-        <v>1.08986889412</v>
+        <v>1.0161743689</v>
       </c>
       <c r="P6">
-        <v>3.02284391388</v>
+        <v>2.8184458911</v>
       </c>
       <c r="Q6">
-        <v>6.90284391388</v>
+        <v>6.6984458911</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09819348600544761</v>
+        <v>0.09860318898560577</v>
       </c>
       <c r="T6">
-        <v>1.210011224144287</v>
+        <v>1.219473186734544</v>
       </c>
       <c r="U6">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V6">
         <v>0.265</v>
       </c>
       <c r="W6">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y6">
-        <v>5.532977919520769</v>
+        <v>4.234929812449806</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -3274,22 +3274,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09579717953632548</v>
+        <v>0.09590712250742123</v>
       </c>
       <c r="C7">
-        <v>395.4472993012956</v>
+        <v>390.5652745284385</v>
       </c>
       <c r="D7">
-        <v>355.6555993012956</v>
+        <v>354.8752345284385</v>
       </c>
       <c r="E7">
-        <v>20.2423</v>
+        <v>24.34396</v>
       </c>
       <c r="F7">
-        <v>20.5083</v>
+        <v>24.60996</v>
       </c>
       <c r="G7">
         <v>60.3</v>
@@ -3310,45 +3310,45 @@
         <v>5.02</v>
       </c>
       <c r="M7">
-        <v>1.18537974</v>
+        <v>1.577498436</v>
       </c>
       <c r="N7">
-        <v>3.83462026</v>
+        <v>3.442501564000001</v>
       </c>
       <c r="O7">
-        <v>1.0161743689</v>
+        <v>0.9122629144600002</v>
       </c>
       <c r="P7">
-        <v>2.8184458911</v>
+        <v>2.53023864954</v>
       </c>
       <c r="Q7">
-        <v>6.6984458911</v>
+        <v>6.41023864954</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09860318898560577</v>
+        <v>0.09902160905044813</v>
       </c>
       <c r="T7">
-        <v>1.219473186734544</v>
+        <v>1.229136467677786</v>
       </c>
       <c r="U7">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V7">
         <v>0.265</v>
       </c>
       <c r="W7">
-        <v>0.042483</v>
+        <v>0.0471135</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.234929812449806</v>
+        <v>3.182253551216833</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3356,22 +3356,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09590712250742123</v>
+        <v>0.096387505478517</v>
       </c>
       <c r="C8">
-        <v>390.5652745284385</v>
+        <v>383.0936911072594</v>
       </c>
       <c r="D8">
-        <v>354.8752345284385</v>
+        <v>351.5053111072594</v>
       </c>
       <c r="E8">
-        <v>24.34396</v>
+        <v>28.44562</v>
       </c>
       <c r="F8">
-        <v>24.60996</v>
+        <v>28.71162</v>
       </c>
       <c r="G8">
         <v>60.3</v>
@@ -3392,45 +3392,45 @@
         <v>5.02</v>
       </c>
       <c r="M8">
-        <v>1.577498436</v>
+        <v>2.176340796</v>
       </c>
       <c r="N8">
-        <v>3.442501564000001</v>
+        <v>2.843659204000001</v>
       </c>
       <c r="O8">
-        <v>0.9122629144600002</v>
+        <v>0.7535696890600002</v>
       </c>
       <c r="P8">
-        <v>2.53023864954</v>
+        <v>2.09008951494</v>
       </c>
       <c r="Q8">
-        <v>6.41023864954</v>
+        <v>5.97008951494</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09902160905044811</v>
+        <v>0.09944902739625483</v>
       </c>
       <c r="T8">
-        <v>1.229136467677785</v>
+        <v>1.23900756111443</v>
       </c>
       <c r="U8">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V8">
         <v>0.265</v>
       </c>
       <c r="W8">
-        <v>0.0471135</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y8">
-        <v>3.182253551216833</v>
+        <v>2.30662404032792</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3438,22 +3438,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09638750547851699</v>
+        <v>0.09635191844961274</v>
       </c>
       <c r="C9">
-        <v>383.0936911072595</v>
+        <v>379.2394802654717</v>
       </c>
       <c r="D9">
-        <v>351.5053111072595</v>
+        <v>351.7527602654717</v>
       </c>
       <c r="E9">
-        <v>28.44562000000001</v>
+        <v>32.54728</v>
       </c>
       <c r="F9">
-        <v>28.71162</v>
+        <v>32.81328</v>
       </c>
       <c r="G9">
         <v>60.3</v>
@@ -3474,28 +3474,28 @@
         <v>5.02</v>
       </c>
       <c r="M9">
-        <v>2.176340796</v>
+        <v>2.487246624</v>
       </c>
       <c r="N9">
-        <v>2.843659204</v>
+        <v>2.532753376000001</v>
       </c>
       <c r="O9">
-        <v>0.7535696890600001</v>
+        <v>0.6711796446400001</v>
       </c>
       <c r="P9">
-        <v>2.09008951494</v>
+        <v>1.86157373136</v>
       </c>
       <c r="Q9">
-        <v>5.97008951494</v>
+        <v>5.741573731360001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09944902739625483</v>
+        <v>0.09988573744523124</v>
       </c>
       <c r="T9">
-        <v>1.23900756111443</v>
+        <v>1.249093243538828</v>
       </c>
       <c r="U9">
         <v>0.07580000000000001</v>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>2.306624040327919</v>
+        <v>2.01829603528693</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -3520,22 +3520,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09635191844961274</v>
+        <v>0.09725566142070849</v>
       </c>
       <c r="C10">
-        <v>379.2394802654717</v>
+        <v>368.9598006680886</v>
       </c>
       <c r="D10">
-        <v>351.7527602654717</v>
+        <v>345.5747406680886</v>
       </c>
       <c r="E10">
-        <v>32.54728</v>
+        <v>36.64894</v>
       </c>
       <c r="F10">
-        <v>32.81328</v>
+        <v>36.91494</v>
       </c>
       <c r="G10">
         <v>60.3</v>
@@ -3556,45 +3556,45 @@
         <v>5.02</v>
       </c>
       <c r="M10">
-        <v>2.487246624</v>
+        <v>3.3223446</v>
       </c>
       <c r="N10">
-        <v>2.532753376000001</v>
+        <v>1.6976554</v>
       </c>
       <c r="O10">
-        <v>0.6711796446400001</v>
+        <v>0.4498786810000001</v>
       </c>
       <c r="P10">
-        <v>1.86157373136</v>
+        <v>1.247776719</v>
       </c>
       <c r="Q10">
-        <v>5.741573731360001</v>
+        <v>5.127776719</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09988573744523124</v>
+        <v>0.1003320455172621</v>
       </c>
       <c r="T10">
-        <v>1.249093243538828</v>
+        <v>1.259400589313212</v>
       </c>
       <c r="U10">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V10">
         <v>0.265</v>
       </c>
       <c r="W10">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.01829603528693</v>
+        <v>1.510981130614808</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3602,22 +3602,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09725566142070849</v>
+        <v>0.1023701366008491</v>
       </c>
       <c r="C11">
-        <v>368.9598006680886</v>
+        <v>333.6149169420929</v>
       </c>
       <c r="D11">
-        <v>345.5747406680886</v>
+        <v>314.3315169420928</v>
       </c>
       <c r="E11">
-        <v>36.64894</v>
+        <v>40.7506</v>
       </c>
       <c r="F11">
-        <v>36.91494</v>
+        <v>41.0166</v>
       </c>
       <c r="G11">
         <v>60.3</v>
@@ -3638,45 +3638,45 @@
         <v>5.02</v>
       </c>
       <c r="M11">
-        <v>3.3223446</v>
+        <v>6.02123688</v>
       </c>
       <c r="N11">
-        <v>1.6976554</v>
+        <v>-1.00123688</v>
       </c>
       <c r="O11">
-        <v>0.4498786810000001</v>
+        <v>-0.2653277731999999</v>
       </c>
       <c r="P11">
-        <v>1.247776719</v>
+        <v>-0.7359091067999997</v>
       </c>
       <c r="Q11">
-        <v>5.127776719</v>
+        <v>3.1440908932</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1003320455172621</v>
+        <v>0.1010371751085709</v>
       </c>
       <c r="T11">
-        <v>1.259400589313212</v>
+        <v>1.27568533738039</v>
       </c>
       <c r="U11">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V11">
-        <v>0.265</v>
+        <v>0.2209346728109458</v>
       </c>
       <c r="W11">
-        <v>0.06615</v>
+        <v>0.1143667900313532</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y11">
-        <v>1.510981130614808</v>
+        <v>0.8337157464563992</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3684,22 +3684,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1023701366008491</v>
+        <v>0.109622180836353</v>
       </c>
       <c r="C12">
-        <v>333.6149169420929</v>
+        <v>293.7961122816479</v>
       </c>
       <c r="D12">
-        <v>314.3315169420928</v>
+        <v>278.6143722816479</v>
       </c>
       <c r="E12">
-        <v>40.75060000000001</v>
+        <v>44.85226</v>
       </c>
       <c r="F12">
-        <v>41.0166</v>
+        <v>45.11826</v>
       </c>
       <c r="G12">
         <v>60.3</v>
@@ -3720,45 +3720,45 @@
         <v>5.02</v>
       </c>
       <c r="M12">
-        <v>6.021236880000001</v>
+        <v>9.059746607999999</v>
       </c>
       <c r="N12">
-        <v>-1.00123688</v>
+        <v>-4.039746607999999</v>
       </c>
       <c r="O12">
-        <v>-0.2653277732000001</v>
+        <v>-1.07053285112</v>
       </c>
       <c r="P12">
-        <v>-0.7359091068000003</v>
+        <v>-2.969213756879999</v>
       </c>
       <c r="Q12">
-        <v>3.1440908932</v>
+        <v>0.9107862431200009</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1010371751085709</v>
+        <v>0.1019971930710311</v>
       </c>
       <c r="T12">
-        <v>1.27568533738039</v>
+        <v>1.297856652910648</v>
       </c>
       <c r="U12">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.2209346728109458</v>
+        <v>0.1468363363303461</v>
       </c>
       <c r="W12">
-        <v>0.1143667900313532</v>
+        <v>0.1713152636648665</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y12">
-        <v>0.8337157464563991</v>
+        <v>0.5540993823786645</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3766,22 +3766,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.109622180836353</v>
+        <v>0.111172180836353</v>
       </c>
       <c r="C13">
-        <v>293.7961122816479</v>
+        <v>283.088396440898</v>
       </c>
       <c r="D13">
-        <v>278.6143722816479</v>
+        <v>272.0083164408979</v>
       </c>
       <c r="E13">
-        <v>44.85226</v>
+        <v>48.95392</v>
       </c>
       <c r="F13">
-        <v>45.11826</v>
+        <v>49.21991999999999</v>
       </c>
       <c r="G13">
         <v>60.3</v>
@@ -3802,37 +3802,37 @@
         <v>5.02</v>
       </c>
       <c r="M13">
-        <v>9.059746607999999</v>
+        <v>9.883359936</v>
       </c>
       <c r="N13">
-        <v>-4.039746607999999</v>
+        <v>-4.863359935999999</v>
       </c>
       <c r="O13">
-        <v>-1.07053285112</v>
+        <v>-1.28879038304</v>
       </c>
       <c r="P13">
-        <v>-2.969213756879999</v>
+        <v>-3.574569552959999</v>
       </c>
       <c r="Q13">
-        <v>0.9107862431200009</v>
+        <v>0.3054304470400004</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1019971930710311</v>
+        <v>0.1026357975377473</v>
       </c>
       <c r="T13">
-        <v>1.297856652910648</v>
+        <v>1.312605023966451</v>
       </c>
       <c r="U13">
         <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.1468363363303461</v>
+        <v>0.1345999749694839</v>
       </c>
       <c r="W13">
-        <v>0.1713152636648665</v>
+        <v>0.1737723250261276</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.5540993823786645</v>
+        <v>0.5079244338471092</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3848,22 +3848,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.111172180836353</v>
+        <v>0.1173940593336686</v>
       </c>
       <c r="C14">
-        <v>283.088396440898</v>
+        <v>255.3478659688789</v>
       </c>
       <c r="D14">
-        <v>272.0083164408979</v>
+        <v>248.3694459688789</v>
       </c>
       <c r="E14">
-        <v>48.95392</v>
+        <v>53.05558000000001</v>
       </c>
       <c r="F14">
-        <v>49.21991999999999</v>
+        <v>53.32158</v>
       </c>
       <c r="G14">
         <v>60.3</v>
@@ -3884,45 +3884,45 @@
         <v>5.02</v>
       </c>
       <c r="M14">
-        <v>9.883359936</v>
+        <v>12.573228564</v>
       </c>
       <c r="N14">
-        <v>-4.863359935999999</v>
+        <v>-7.553228564</v>
       </c>
       <c r="O14">
-        <v>-1.28879038304</v>
+        <v>-2.00160556946</v>
       </c>
       <c r="P14">
-        <v>-3.574569552959999</v>
+        <v>-5.551622994540001</v>
       </c>
       <c r="Q14">
-        <v>0.3054304470400004</v>
+        <v>-1.671622994540001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1026357975377473</v>
+        <v>0.1034291727937164</v>
       </c>
       <c r="T14">
-        <v>1.312605023966451</v>
+        <v>1.330927778145875</v>
       </c>
       <c r="U14">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.1345999749694839</v>
+        <v>0.1058041690110486</v>
       </c>
       <c r="W14">
-        <v>0.1737723250261276</v>
+        <v>0.2108513769471947</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y14">
-        <v>0.5079244338471092</v>
+        <v>0.3992610151360325</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3930,22 +3930,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1173940593336686</v>
+        <v>0.1192940593336686</v>
       </c>
       <c r="C15">
-        <v>255.3478659688789</v>
+        <v>244.8252523350838</v>
       </c>
       <c r="D15">
-        <v>248.3694459688789</v>
+        <v>241.9484923350838</v>
       </c>
       <c r="E15">
-        <v>53.05558000000001</v>
+        <v>57.15724000000001</v>
       </c>
       <c r="F15">
-        <v>53.32158</v>
+        <v>57.42324000000001</v>
       </c>
       <c r="G15">
         <v>60.3</v>
@@ -3966,37 +3966,37 @@
         <v>5.02</v>
       </c>
       <c r="M15">
-        <v>12.573228564</v>
+        <v>13.540399992</v>
       </c>
       <c r="N15">
-        <v>-7.553228564</v>
+        <v>-8.520399992000002</v>
       </c>
       <c r="O15">
-        <v>-2.00160556946</v>
+        <v>-2.25790599788</v>
       </c>
       <c r="P15">
-        <v>-5.551622994540001</v>
+        <v>-6.262493994120002</v>
       </c>
       <c r="Q15">
-        <v>-1.671622994540001</v>
+        <v>-2.382493994120002</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1034291727937164</v>
+        <v>0.1040992794541084</v>
       </c>
       <c r="T15">
-        <v>1.330927778145875</v>
+        <v>1.34640368254292</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.1058041690110486</v>
+        <v>0.09824672836740227</v>
       </c>
       <c r="W15">
-        <v>0.2108513769471947</v>
+        <v>0.2126334214509666</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3992610151360325</v>
+        <v>0.3707423711977444</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -4012,22 +4012,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1192940593336686</v>
+        <v>0.1211940593336686</v>
       </c>
       <c r="C16">
-        <v>244.8252523350838</v>
+        <v>234.6262666372834</v>
       </c>
       <c r="D16">
-        <v>241.9484923350838</v>
+        <v>235.8511666372835</v>
       </c>
       <c r="E16">
-        <v>57.15724000000001</v>
+        <v>61.25890000000001</v>
       </c>
       <c r="F16">
-        <v>57.42324000000001</v>
+        <v>61.52490000000001</v>
       </c>
       <c r="G16">
         <v>60.3</v>
@@ -4048,37 +4048,37 @@
         <v>5.02</v>
       </c>
       <c r="M16">
-        <v>13.540399992</v>
+        <v>14.50757142</v>
       </c>
       <c r="N16">
-        <v>-8.520399992000002</v>
+        <v>-9.487571420000002</v>
       </c>
       <c r="O16">
-        <v>-2.25790599788</v>
+        <v>-2.514206426300001</v>
       </c>
       <c r="P16">
-        <v>-6.262493994120002</v>
+        <v>-6.973364993700001</v>
       </c>
       <c r="Q16">
-        <v>-2.382493994120002</v>
+        <v>-3.093364993700001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1040992794541084</v>
+        <v>0.1047851533300391</v>
       </c>
       <c r="T16">
-        <v>1.34640368254292</v>
+        <v>1.362243725866954</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.09824672836740227</v>
+        <v>0.09169694647624212</v>
       </c>
       <c r="W16">
-        <v>0.2126334214509666</v>
+        <v>0.2141778600209021</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3707423711977444</v>
+        <v>0.3460262131178948</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -4094,22 +4094,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1211940593336686</v>
+        <v>0.1230940593336686</v>
       </c>
       <c r="C17">
-        <v>234.6262666372835</v>
+        <v>224.7270431443847</v>
       </c>
       <c r="D17">
-        <v>235.8511666372836</v>
+        <v>230.0536031443847</v>
       </c>
       <c r="E17">
-        <v>61.2589</v>
+        <v>65.36055999999999</v>
       </c>
       <c r="F17">
-        <v>61.5249</v>
+        <v>65.62656</v>
       </c>
       <c r="G17">
         <v>60.3</v>
@@ -4130,37 +4130,37 @@
         <v>5.02</v>
       </c>
       <c r="M17">
-        <v>14.50757142</v>
+        <v>15.474742848</v>
       </c>
       <c r="N17">
-        <v>-9.487571419999998</v>
+        <v>-10.454742848</v>
       </c>
       <c r="O17">
-        <v>-2.514206426299999</v>
+        <v>-2.77050685472</v>
       </c>
       <c r="P17">
-        <v>-6.973364993699999</v>
+        <v>-7.684235993279999</v>
       </c>
       <c r="Q17">
-        <v>-3.093364993699999</v>
+        <v>-3.804235993279999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1047851533300391</v>
+        <v>0.1054873575363491</v>
       </c>
       <c r="T17">
-        <v>1.362243725866954</v>
+        <v>1.378460913079656</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.09169694647624214</v>
+        <v>0.08596588732147702</v>
       </c>
       <c r="W17">
-        <v>0.2141778600209021</v>
+        <v>0.2155292437695957</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3460262131178949</v>
+        <v>0.3243995747980265</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -4176,22 +4176,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1230940593336686</v>
+        <v>0.1249940593336686</v>
       </c>
       <c r="C18">
-        <v>224.7270431443847</v>
+        <v>215.1060064429998</v>
       </c>
       <c r="D18">
-        <v>230.0536031443847</v>
+        <v>224.5342264429999</v>
       </c>
       <c r="E18">
-        <v>65.36055999999999</v>
+        <v>69.46222</v>
       </c>
       <c r="F18">
-        <v>65.62656</v>
+        <v>69.72822000000001</v>
       </c>
       <c r="G18">
         <v>60.3</v>
@@ -4212,37 +4212,37 @@
         <v>5.02</v>
       </c>
       <c r="M18">
-        <v>15.474742848</v>
+        <v>16.441914276</v>
       </c>
       <c r="N18">
-        <v>-10.454742848</v>
+        <v>-11.421914276</v>
       </c>
       <c r="O18">
-        <v>-2.77050685472</v>
+        <v>-3.026807283140001</v>
       </c>
       <c r="P18">
-        <v>-7.684235993279999</v>
+        <v>-8.395106992860001</v>
       </c>
       <c r="Q18">
-        <v>-3.804235993279999</v>
+        <v>-4.515106992860001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1054873575363491</v>
+        <v>0.1062064823259437</v>
       </c>
       <c r="T18">
-        <v>1.378460913079656</v>
+        <v>1.395068875887844</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.08596588732147702</v>
+        <v>0.08090907042021366</v>
       </c>
       <c r="W18">
-        <v>0.2155292437695957</v>
+        <v>0.2167216411949136</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3243995747980265</v>
+        <v>0.3053172468687306</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -4258,22 +4258,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1249940593336686</v>
+        <v>0.1268940593336686</v>
       </c>
       <c r="C19">
-        <v>215.1060064429998</v>
+        <v>205.7436031315033</v>
       </c>
       <c r="D19">
-        <v>224.5342264429999</v>
+        <v>219.2734831315034</v>
       </c>
       <c r="E19">
-        <v>69.46222</v>
+        <v>73.56388</v>
       </c>
       <c r="F19">
-        <v>69.72822000000001</v>
+        <v>73.82988</v>
       </c>
       <c r="G19">
         <v>60.3</v>
@@ -4294,37 +4294,37 @@
         <v>5.02</v>
       </c>
       <c r="M19">
-        <v>16.441914276</v>
+        <v>17.409085704</v>
       </c>
       <c r="N19">
-        <v>-11.421914276</v>
+        <v>-12.389085704</v>
       </c>
       <c r="O19">
-        <v>-3.026807283140001</v>
+        <v>-3.283107711560001</v>
       </c>
       <c r="P19">
-        <v>-8.395106992860001</v>
+        <v>-9.105977992440002</v>
       </c>
       <c r="Q19">
-        <v>-4.515106992860001</v>
+        <v>-5.225977992440002</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1062064823259437</v>
+        <v>0.1069431467445527</v>
       </c>
       <c r="T19">
-        <v>1.395068875887844</v>
+        <v>1.412081910959648</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.08090907042021366</v>
+        <v>0.07641412206353511</v>
       </c>
       <c r="W19">
-        <v>0.2167216411949136</v>
+        <v>0.2177815500174184</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3053172468687306</v>
+        <v>0.2883551775982456</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -4340,22 +4340,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1268940593336686</v>
+        <v>0.1287940593336686</v>
       </c>
       <c r="C20">
-        <v>205.7436031315033</v>
+        <v>196.6220703683832</v>
       </c>
       <c r="D20">
-        <v>219.2734831315034</v>
+        <v>214.2536103683832</v>
       </c>
       <c r="E20">
-        <v>73.56388</v>
+        <v>77.66553999999999</v>
       </c>
       <c r="F20">
-        <v>73.82988</v>
+        <v>77.93154</v>
       </c>
       <c r="G20">
         <v>60.3</v>
@@ -4376,37 +4376,37 @@
         <v>5.02</v>
       </c>
       <c r="M20">
-        <v>17.409085704</v>
+        <v>18.376257132</v>
       </c>
       <c r="N20">
-        <v>-12.389085704</v>
+        <v>-13.356257132</v>
       </c>
       <c r="O20">
-        <v>-3.283107711560001</v>
+        <v>-3.53940813998</v>
       </c>
       <c r="P20">
-        <v>-9.105977992440002</v>
+        <v>-9.816848992019999</v>
       </c>
       <c r="Q20">
-        <v>-5.225977992440002</v>
+        <v>-5.936848992019999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1069431467445527</v>
+        <v>0.1076980004080657</v>
       </c>
       <c r="T20">
-        <v>1.412081910959648</v>
+        <v>1.429515020971495</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07641412206353511</v>
+        <v>0.07239232616545432</v>
       </c>
       <c r="W20">
-        <v>0.2177815500174184</v>
+        <v>0.2187298894901859</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2883551775982456</v>
+        <v>0.2731785893036012</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -4422,22 +4422,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1287940593336686</v>
+        <v>0.1306940593336686</v>
       </c>
       <c r="C21">
-        <v>196.6220703683832</v>
+        <v>187.7252355010827</v>
       </c>
       <c r="D21">
-        <v>214.2536103683832</v>
+        <v>209.4584355010827</v>
       </c>
       <c r="E21">
-        <v>77.66553999999999</v>
+        <v>81.7672</v>
       </c>
       <c r="F21">
-        <v>77.93154</v>
+        <v>82.03320000000001</v>
       </c>
       <c r="G21">
         <v>60.3</v>
@@ -4458,37 +4458,37 @@
         <v>5.02</v>
       </c>
       <c r="M21">
-        <v>18.376257132</v>
+        <v>19.34342856</v>
       </c>
       <c r="N21">
-        <v>-13.356257132</v>
+        <v>-14.32342856</v>
       </c>
       <c r="O21">
-        <v>-3.53940813998</v>
+        <v>-3.795708568400001</v>
       </c>
       <c r="P21">
-        <v>-9.816848992019999</v>
+        <v>-10.5277199916</v>
       </c>
       <c r="Q21">
-        <v>-5.936848992019999</v>
+        <v>-6.647719991600002</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1076980004080657</v>
+        <v>0.1084717254131665</v>
       </c>
       <c r="T21">
-        <v>1.429515020971495</v>
+        <v>1.447383958733639</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.07239232616545432</v>
+        <v>0.0687727098571816</v>
       </c>
       <c r="W21">
-        <v>0.2187298894901859</v>
+        <v>0.2195833950156766</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2731785893036012</v>
+        <v>0.2595196598384211</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -4504,22 +4504,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1306940593336686</v>
+        <v>0.1325940593336686</v>
       </c>
       <c r="C22">
-        <v>187.7252355010827</v>
+        <v>179.0383420126695</v>
       </c>
       <c r="D22">
-        <v>209.4584355010827</v>
+        <v>204.8732020126696</v>
       </c>
       <c r="E22">
-        <v>81.7672</v>
+        <v>85.86886</v>
       </c>
       <c r="F22">
-        <v>82.03320000000001</v>
+        <v>86.13486</v>
       </c>
       <c r="G22">
         <v>60.3</v>
@@ -4540,37 +4540,37 @@
         <v>5.02</v>
       </c>
       <c r="M22">
-        <v>19.34342856</v>
+        <v>20.310599988</v>
       </c>
       <c r="N22">
-        <v>-14.32342856</v>
+        <v>-15.290599988</v>
       </c>
       <c r="O22">
-        <v>-3.795708568400001</v>
+        <v>-4.052008996820001</v>
       </c>
       <c r="P22">
-        <v>-10.5277199916</v>
+        <v>-11.23859099118</v>
       </c>
       <c r="Q22">
-        <v>-6.647719991600002</v>
+        <v>-7.358590991180001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1084717254131665</v>
+        <v>0.10926503839308</v>
       </c>
       <c r="T22">
-        <v>1.447383958733639</v>
+        <v>1.465705274666976</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.0687727098571816</v>
+        <v>0.06549781891160153</v>
       </c>
       <c r="W22">
-        <v>0.2195833950156766</v>
+        <v>0.2203556143006443</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2595196598384211</v>
+        <v>0.2471615807984963</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -4586,22 +4586,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1325940593336686</v>
+        <v>0.1344940593336686</v>
       </c>
       <c r="C23">
-        <v>179.0383420126695</v>
+        <v>170.5478978398799</v>
       </c>
       <c r="D23">
-        <v>204.8732020126696</v>
+        <v>200.4844178398799</v>
       </c>
       <c r="E23">
-        <v>85.86885999999998</v>
+        <v>89.97051999999999</v>
       </c>
       <c r="F23">
-        <v>86.13485999999999</v>
+        <v>90.23652</v>
       </c>
       <c r="G23">
         <v>60.3</v>
@@ -4622,37 +4622,37 @@
         <v>5.02</v>
       </c>
       <c r="M23">
-        <v>20.310599988</v>
+        <v>21.277771416</v>
       </c>
       <c r="N23">
-        <v>-15.290599988</v>
+        <v>-16.257771416</v>
       </c>
       <c r="O23">
-        <v>-4.052008996820001</v>
+        <v>-4.30830942524</v>
       </c>
       <c r="P23">
-        <v>-11.23859099118</v>
+        <v>-11.94946199076</v>
       </c>
       <c r="Q23">
-        <v>-7.358590991180001</v>
+        <v>-8.069461990760001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.10926503839308</v>
+        <v>0.1100786927314529</v>
       </c>
       <c r="T23">
-        <v>1.465705274666976</v>
+        <v>1.484496367931937</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.06549781891160153</v>
+        <v>0.06252064532471055</v>
       </c>
       <c r="W23">
-        <v>0.2203556143006443</v>
+        <v>0.2210576318324333</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2471615807984963</v>
+        <v>0.2359269634894737</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -4668,22 +4668,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1344940593336686</v>
+        <v>0.1363940593336686</v>
       </c>
       <c r="C24">
-        <v>170.5478978398799</v>
+        <v>162.2415427782225</v>
       </c>
       <c r="D24">
-        <v>200.4844178398799</v>
+        <v>196.2797227782225</v>
       </c>
       <c r="E24">
-        <v>89.97051999999999</v>
+        <v>94.07218</v>
       </c>
       <c r="F24">
-        <v>90.23652</v>
+        <v>94.33818000000001</v>
       </c>
       <c r="G24">
         <v>60.3</v>
@@ -4704,37 +4704,37 @@
         <v>5.02</v>
       </c>
       <c r="M24">
-        <v>21.277771416</v>
+        <v>22.244942844</v>
       </c>
       <c r="N24">
-        <v>-16.257771416</v>
+        <v>-17.224942844</v>
       </c>
       <c r="O24">
-        <v>-4.30830942524</v>
+        <v>-4.564609853660001</v>
       </c>
       <c r="P24">
-        <v>-11.94946199076</v>
+        <v>-12.66033299034</v>
       </c>
       <c r="Q24">
-        <v>-8.069461990760001</v>
+        <v>-8.780332990340003</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1100786927314529</v>
+        <v>0.1109134809487445</v>
       </c>
       <c r="T24">
-        <v>1.484496367931937</v>
+        <v>1.503775541541443</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.06252064532471055</v>
+        <v>0.05980235639754921</v>
       </c>
       <c r="W24">
-        <v>0.2210576318324333</v>
+        <v>0.2216986043614579</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2359269634894737</v>
+        <v>0.225669269424714</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -4750,22 +4750,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1363940593336686</v>
+        <v>0.1382940593336686</v>
       </c>
       <c r="C25">
-        <v>162.2415427782225</v>
+        <v>154.1079322295576</v>
       </c>
       <c r="D25">
-        <v>196.2797227782225</v>
+        <v>192.2477722295576</v>
       </c>
       <c r="E25">
-        <v>94.07218</v>
+        <v>98.17384</v>
       </c>
       <c r="F25">
-        <v>94.33818000000001</v>
+        <v>98.43984</v>
       </c>
       <c r="G25">
         <v>60.3</v>
@@ -4786,37 +4786,37 @@
         <v>5.02</v>
       </c>
       <c r="M25">
-        <v>22.244942844</v>
+        <v>23.212114272</v>
       </c>
       <c r="N25">
-        <v>-17.224942844</v>
+        <v>-18.192114272</v>
       </c>
       <c r="O25">
-        <v>-4.564609853660001</v>
+        <v>-4.820910282080001</v>
       </c>
       <c r="P25">
-        <v>-12.66033299034</v>
+        <v>-13.37120398992</v>
       </c>
       <c r="Q25">
-        <v>-8.780332990340003</v>
+        <v>-9.491203989920002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1109134809487445</v>
+        <v>0.1117702372770174</v>
       </c>
       <c r="T25">
-        <v>1.503775541541443</v>
+        <v>1.523562061824883</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.05980235639754921</v>
+        <v>0.05731059154765134</v>
       </c>
       <c r="W25">
-        <v>0.2216986043614579</v>
+        <v>0.2222861625130639</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.225669269424714</v>
+        <v>0.2162663831986842</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -4832,22 +4832,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1382940593336686</v>
+        <v>0.1401940593336685</v>
       </c>
       <c r="C26">
-        <v>154.1079322295577</v>
+        <v>146.1366349895172</v>
       </c>
       <c r="D26">
-        <v>192.2477722295577</v>
+        <v>188.3781349895172</v>
       </c>
       <c r="E26">
-        <v>98.17383999999998</v>
+        <v>102.2755</v>
       </c>
       <c r="F26">
-        <v>98.43983999999999</v>
+        <v>102.5415</v>
       </c>
       <c r="G26">
         <v>60.3</v>
@@ -4868,37 +4868,37 @@
         <v>5.02</v>
       </c>
       <c r="M26">
-        <v>23.212114272</v>
+        <v>24.1792857</v>
       </c>
       <c r="N26">
-        <v>-18.192114272</v>
+        <v>-19.1592857</v>
       </c>
       <c r="O26">
-        <v>-4.82091028208</v>
+        <v>-5.077210710500001</v>
       </c>
       <c r="P26">
-        <v>-13.37120398992</v>
+        <v>-14.0820749895</v>
       </c>
       <c r="Q26">
-        <v>-9.491203989919999</v>
+        <v>-10.2020749895</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1117702372770174</v>
+        <v>0.112649840440711</v>
       </c>
       <c r="T26">
-        <v>1.523562061824883</v>
+        <v>1.543876222649215</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05731059154765134</v>
+        <v>0.05501816788574528</v>
       </c>
       <c r="W26">
-        <v>0.2222861625130638</v>
+        <v>0.2228267160125413</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2162663831986843</v>
+        <v>0.2076157278707369</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -4914,22 +4914,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1401940593336685</v>
+        <v>0.1420940593336686</v>
       </c>
       <c r="C27">
-        <v>146.1366349895172</v>
+        <v>138.3180431356022</v>
       </c>
       <c r="D27">
-        <v>188.3781349895172</v>
+        <v>184.6612031356023</v>
       </c>
       <c r="E27">
-        <v>102.2755</v>
+        <v>106.37716</v>
       </c>
       <c r="F27">
-        <v>102.5415</v>
+        <v>106.64316</v>
       </c>
       <c r="G27">
         <v>60.3</v>
@@ -4950,37 +4950,37 @@
         <v>5.02</v>
       </c>
       <c r="M27">
-        <v>24.1792857</v>
+        <v>25.146457128</v>
       </c>
       <c r="N27">
-        <v>-19.1592857</v>
+        <v>-20.126457128</v>
       </c>
       <c r="O27">
-        <v>-5.077210710500001</v>
+        <v>-5.333511138920001</v>
       </c>
       <c r="P27">
-        <v>-14.0820749895</v>
+        <v>-14.79294598908</v>
       </c>
       <c r="Q27">
-        <v>-10.2020749895</v>
+        <v>-10.91294598908</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.112649840440711</v>
+        <v>0.1135532166628828</v>
       </c>
       <c r="T27">
-        <v>1.543876222649215</v>
+        <v>1.564739414847177</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.05501816788574528</v>
+        <v>0.05290208450552431</v>
       </c>
       <c r="W27">
-        <v>0.2228267160125413</v>
+        <v>0.2233256884735974</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2076157278707369</v>
+        <v>0.1996305075680163</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4996,22 +4996,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1420940593336686</v>
+        <v>0.1439940593336686</v>
       </c>
       <c r="C28">
-        <v>138.3180431356022</v>
+        <v>130.6432923769707</v>
       </c>
       <c r="D28">
-        <v>184.6612031356023</v>
+        <v>181.0881123769707</v>
       </c>
       <c r="E28">
-        <v>106.37716</v>
+        <v>110.47882</v>
       </c>
       <c r="F28">
-        <v>106.64316</v>
+        <v>110.74482</v>
       </c>
       <c r="G28">
         <v>60.3</v>
@@ -5032,37 +5032,37 @@
         <v>5.02</v>
       </c>
       <c r="M28">
-        <v>25.146457128</v>
+        <v>26.113628556</v>
       </c>
       <c r="N28">
-        <v>-20.126457128</v>
+        <v>-21.093628556</v>
       </c>
       <c r="O28">
-        <v>-5.333511138920001</v>
+        <v>-5.589811567340001</v>
       </c>
       <c r="P28">
-        <v>-14.79294598908</v>
+        <v>-15.50381698866</v>
       </c>
       <c r="Q28">
-        <v>-10.91294598908</v>
+        <v>-11.62381698866</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1135532166628828</v>
+        <v>0.1144813429185387</v>
       </c>
       <c r="T28">
-        <v>1.564739414847177</v>
+        <v>1.586174201351933</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.05290208450552431</v>
+        <v>0.05094274804235674</v>
       </c>
       <c r="W28">
-        <v>0.2233256884735974</v>
+        <v>0.2237877000116123</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1996305075680163</v>
+        <v>0.1922367850654971</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -5078,22 +5078,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1439940593336686</v>
+        <v>0.1458940593336686</v>
       </c>
       <c r="C29">
-        <v>130.6432923769707</v>
+        <v>123.1041914758152</v>
       </c>
       <c r="D29">
-        <v>181.0881123769707</v>
+        <v>177.6506714758152</v>
       </c>
       <c r="E29">
-        <v>110.47882</v>
+        <v>114.58048</v>
       </c>
       <c r="F29">
-        <v>110.74482</v>
+        <v>114.84648</v>
       </c>
       <c r="G29">
         <v>60.3</v>
@@ -5114,37 +5114,37 @@
         <v>5.02</v>
       </c>
       <c r="M29">
-        <v>26.113628556</v>
+        <v>27.08079998400001</v>
       </c>
       <c r="N29">
-        <v>-21.093628556</v>
+        <v>-22.06079998400001</v>
       </c>
       <c r="O29">
-        <v>-5.589811567340001</v>
+        <v>-5.846111995760002</v>
       </c>
       <c r="P29">
-        <v>-15.50381698866</v>
+        <v>-16.21468798824001</v>
       </c>
       <c r="Q29">
-        <v>-11.62381698866</v>
+        <v>-12.33468798824001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1144813429185387</v>
+        <v>0.115435250459074</v>
       </c>
       <c r="T29">
-        <v>1.586174201351933</v>
+        <v>1.608204398592932</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05094274804235674</v>
+        <v>0.04912336418370113</v>
       </c>
       <c r="W29">
-        <v>0.2237877000116123</v>
+        <v>0.2242167107254833</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1922367850654971</v>
+        <v>0.1853711855988722</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -5160,22 +5160,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1458940593336686</v>
+        <v>0.1477940593336686</v>
       </c>
       <c r="C30">
-        <v>123.1041914758152</v>
+        <v>115.6931595573997</v>
       </c>
       <c r="D30">
-        <v>177.6506714758152</v>
+        <v>174.3412995573997</v>
       </c>
       <c r="E30">
-        <v>114.58048</v>
+        <v>118.68214</v>
       </c>
       <c r="F30">
-        <v>114.84648</v>
+        <v>118.94814</v>
       </c>
       <c r="G30">
         <v>60.3</v>
@@ -5196,37 +5196,37 @@
         <v>5.02</v>
       </c>
       <c r="M30">
-        <v>27.08079998400001</v>
+        <v>28.047971412</v>
       </c>
       <c r="N30">
-        <v>-22.06079998400001</v>
+        <v>-23.027971412</v>
       </c>
       <c r="O30">
-        <v>-5.846111995760002</v>
+        <v>-6.102412424180002</v>
       </c>
       <c r="P30">
-        <v>-16.21468798824001</v>
+        <v>-16.92555898782</v>
       </c>
       <c r="Q30">
-        <v>-12.33468798824001</v>
+        <v>-13.04555898782</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.115435250459074</v>
+        <v>0.1164160286345539</v>
       </c>
       <c r="T30">
-        <v>1.608204398592932</v>
+        <v>1.630855164770297</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04912336418370113</v>
+        <v>0.04742945507391835</v>
       </c>
       <c r="W30">
-        <v>0.2242167107254833</v>
+        <v>0.2246161344935701</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1853711855988722</v>
+        <v>0.1789790757506352</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -5242,22 +5242,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1477940593336686</v>
+        <v>0.1496940593336686</v>
       </c>
       <c r="C31">
-        <v>115.6931595573997</v>
+        <v>108.4031702988882</v>
       </c>
       <c r="D31">
-        <v>174.3412995573997</v>
+        <v>171.1529702988882</v>
       </c>
       <c r="E31">
-        <v>118.68214</v>
+        <v>122.7838</v>
       </c>
       <c r="F31">
-        <v>118.94814</v>
+        <v>123.0498</v>
       </c>
       <c r="G31">
         <v>60.3</v>
@@ -5278,37 +5278,37 @@
         <v>5.02</v>
       </c>
       <c r="M31">
-        <v>28.047971412</v>
+        <v>29.01514284</v>
       </c>
       <c r="N31">
-        <v>-23.027971412</v>
+        <v>-23.99514284</v>
       </c>
       <c r="O31">
-        <v>-6.10241242418</v>
+        <v>-6.3587128526</v>
       </c>
       <c r="P31">
-        <v>-16.92555898782</v>
+        <v>-17.6364299874</v>
       </c>
       <c r="Q31">
-        <v>-13.04555898782</v>
+        <v>-13.7564299874</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1164160286345539</v>
+        <v>0.1174248290436189</v>
       </c>
       <c r="T31">
-        <v>1.630855164770297</v>
+        <v>1.654153095695587</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04742945507391835</v>
+        <v>0.04584847323812107</v>
       </c>
       <c r="W31">
-        <v>0.2246161344935701</v>
+        <v>0.2249889300104511</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1789790757506352</v>
+        <v>0.1730131065589474</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -5324,22 +5324,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1496940593336686</v>
+        <v>0.1515940593336685</v>
       </c>
       <c r="C32">
-        <v>108.4031702988882</v>
+        <v>101.227702132191</v>
       </c>
       <c r="D32">
-        <v>171.1529702988882</v>
+        <v>168.079162132191</v>
       </c>
       <c r="E32">
-        <v>122.7838</v>
+        <v>126.88546</v>
       </c>
       <c r="F32">
-        <v>123.0498</v>
+        <v>127.15146</v>
       </c>
       <c r="G32">
         <v>60.3</v>
@@ -5360,37 +5360,37 @@
         <v>5.02</v>
       </c>
       <c r="M32">
-        <v>29.01514284</v>
+        <v>29.982314268</v>
       </c>
       <c r="N32">
-        <v>-23.99514284</v>
+        <v>-24.962314268</v>
       </c>
       <c r="O32">
-        <v>-6.3587128526</v>
+        <v>-6.61501328102</v>
       </c>
       <c r="P32">
-        <v>-17.6364299874</v>
+        <v>-18.34730098698</v>
       </c>
       <c r="Q32">
-        <v>-13.7564299874</v>
+        <v>-14.46730098698</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1174248290436189</v>
+        <v>0.1184628700442511</v>
       </c>
       <c r="T32">
-        <v>1.654153095695587</v>
+        <v>1.678126328966538</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.04584847323812107</v>
+        <v>0.04436949023043974</v>
       </c>
       <c r="W32">
-        <v>0.2249889300104511</v>
+        <v>0.2253376742036623</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1730131065589474</v>
+        <v>0.167432038605433</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -5406,22 +5406,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1515940593336685</v>
+        <v>0.1534940593336686</v>
       </c>
       <c r="C33">
-        <v>101.227702132191</v>
+        <v>94.16069371810883</v>
       </c>
       <c r="D33">
-        <v>168.079162132191</v>
+        <v>165.1138137181088</v>
       </c>
       <c r="E33">
-        <v>126.88546</v>
+        <v>130.98712</v>
       </c>
       <c r="F33">
-        <v>127.15146</v>
+        <v>131.25312</v>
       </c>
       <c r="G33">
         <v>60.3</v>
@@ -5442,37 +5442,37 @@
         <v>5.02</v>
       </c>
       <c r="M33">
-        <v>29.982314268</v>
+        <v>30.949485696</v>
       </c>
       <c r="N33">
-        <v>-24.962314268</v>
+        <v>-25.929485696</v>
       </c>
       <c r="O33">
-        <v>-6.61501328102</v>
+        <v>-6.871313709440001</v>
       </c>
       <c r="P33">
-        <v>-18.34730098698</v>
+        <v>-19.05817198656</v>
       </c>
       <c r="Q33">
-        <v>-14.46730098698</v>
+        <v>-15.17817198656</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1184628700442511</v>
+        <v>0.1195314416625489</v>
       </c>
       <c r="T33">
-        <v>1.678126328966538</v>
+        <v>1.702804657333693</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.04436949023043974</v>
+        <v>0.04298294366073851</v>
       </c>
       <c r="W33">
-        <v>0.2253376742036623</v>
+        <v>0.2256646218847979</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.167432038605433</v>
+        <v>0.1621997873990132</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -5488,22 +5488,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1534940593336686</v>
+        <v>0.1553940593336686</v>
       </c>
       <c r="C34">
-        <v>94.16069371810883</v>
+        <v>87.19650405206846</v>
       </c>
       <c r="D34">
-        <v>165.1138137181088</v>
+        <v>162.2512840520685</v>
       </c>
       <c r="E34">
-        <v>130.98712</v>
+        <v>135.08878</v>
       </c>
       <c r="F34">
-        <v>131.25312</v>
+        <v>135.35478</v>
       </c>
       <c r="G34">
         <v>60.3</v>
@@ -5524,37 +5524,37 @@
         <v>5.02</v>
       </c>
       <c r="M34">
-        <v>30.949485696</v>
+        <v>31.916657124</v>
       </c>
       <c r="N34">
-        <v>-25.929485696</v>
+        <v>-26.896657124</v>
       </c>
       <c r="O34">
-        <v>-6.871313709440001</v>
+        <v>-7.127614137860001</v>
       </c>
       <c r="P34">
-        <v>-19.05817198656</v>
+        <v>-19.76904298614</v>
       </c>
       <c r="Q34">
-        <v>-15.17817198656</v>
+        <v>-15.88904298614001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1195314416625489</v>
+        <v>0.1206319109410944</v>
       </c>
       <c r="T34">
-        <v>1.702804657333693</v>
+        <v>1.72821965221927</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04298294366073851</v>
+        <v>0.04168043021647369</v>
       </c>
       <c r="W34">
-        <v>0.2256646218847979</v>
+        <v>0.2259717545549555</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1621997873990132</v>
+        <v>0.1572846423263158</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -5570,22 +5570,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1553940593336686</v>
+        <v>0.1572940593336686</v>
       </c>
       <c r="C35">
-        <v>87.19650405206846</v>
+        <v>80.32987664895015</v>
       </c>
       <c r="D35">
-        <v>162.2512840520685</v>
+        <v>159.4863166489502</v>
       </c>
       <c r="E35">
-        <v>135.08878</v>
+        <v>139.19044</v>
       </c>
       <c r="F35">
-        <v>135.35478</v>
+        <v>139.45644</v>
       </c>
       <c r="G35">
         <v>60.3</v>
@@ -5606,37 +5606,37 @@
         <v>5.02</v>
       </c>
       <c r="M35">
-        <v>31.916657124</v>
+        <v>32.883828552</v>
       </c>
       <c r="N35">
-        <v>-26.896657124</v>
+        <v>-27.863828552</v>
       </c>
       <c r="O35">
-        <v>-7.127614137860001</v>
+        <v>-7.383914566280001</v>
       </c>
       <c r="P35">
-        <v>-19.76904298614</v>
+        <v>-20.47991398572</v>
       </c>
       <c r="Q35">
-        <v>-15.88904298614001</v>
+        <v>-16.59991398572</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1206319109410944</v>
+        <v>0.1217657277735352</v>
       </c>
       <c r="T35">
-        <v>1.72821965221927</v>
+        <v>1.754404798465017</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04168043021647369</v>
+        <v>0.04045453521010683</v>
       </c>
       <c r="W35">
-        <v>0.2259717545549555</v>
+        <v>0.2262608205974568</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1572846423263158</v>
+        <v>0.1526586234343653</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -5652,22 +5652,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1572940593336686</v>
+        <v>0.1591940593336685</v>
       </c>
       <c r="C36">
-        <v>80.32987664895015</v>
+        <v>73.55590732857092</v>
       </c>
       <c r="D36">
-        <v>159.4863166489502</v>
+        <v>156.814007328571</v>
       </c>
       <c r="E36">
-        <v>139.19044</v>
+        <v>143.2921</v>
       </c>
       <c r="F36">
-        <v>139.45644</v>
+        <v>143.5581</v>
       </c>
       <c r="G36">
         <v>60.3</v>
@@ -5688,37 +5688,37 @@
         <v>5.02</v>
       </c>
       <c r="M36">
-        <v>32.883828552</v>
+        <v>33.85099998</v>
       </c>
       <c r="N36">
-        <v>-27.863828552</v>
+        <v>-28.83099998</v>
       </c>
       <c r="O36">
-        <v>-7.383914566280001</v>
+        <v>-7.640214994700002</v>
       </c>
       <c r="P36">
-        <v>-20.47991398572</v>
+        <v>-21.1907849853</v>
       </c>
       <c r="Q36">
-        <v>-16.59991398572</v>
+        <v>-17.3107849853</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1217657277735352</v>
+        <v>0.1229344312777435</v>
       </c>
       <c r="T36">
-        <v>1.754404798465017</v>
+        <v>1.781395641518325</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04045453521010683</v>
+        <v>0.03929869134696092</v>
       </c>
       <c r="W36">
-        <v>0.2262608205974568</v>
+        <v>0.2265333685803866</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1526586234343653</v>
+        <v>0.1482969484790978</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -5734,22 +5734,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1591940593336685</v>
+        <v>0.1610940593336686</v>
       </c>
       <c r="C37">
-        <v>73.55590732857092</v>
+        <v>66.8700151864619</v>
       </c>
       <c r="D37">
-        <v>156.814007328571</v>
+        <v>154.2297751864619</v>
       </c>
       <c r="E37">
-        <v>143.2921</v>
+        <v>147.39376</v>
       </c>
       <c r="F37">
-        <v>143.5581</v>
+        <v>147.65976</v>
       </c>
       <c r="G37">
         <v>60.3</v>
@@ -5770,37 +5770,37 @@
         <v>5.02</v>
       </c>
       <c r="M37">
-        <v>33.85099998</v>
+        <v>34.818171408</v>
       </c>
       <c r="N37">
-        <v>-28.83099998</v>
+        <v>-29.79817140800001</v>
       </c>
       <c r="O37">
-        <v>-7.640214994700002</v>
+        <v>-7.896515423120002</v>
       </c>
       <c r="P37">
-        <v>-21.1907849853</v>
+        <v>-21.90165598488</v>
       </c>
       <c r="Q37">
-        <v>-17.3107849853</v>
+        <v>-18.02165598488</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1229344312777435</v>
+        <v>0.1241396567664582</v>
       </c>
       <c r="T37">
-        <v>1.781395641518325</v>
+        <v>1.809229948417048</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03929869134696092</v>
+        <v>0.03820706103176755</v>
       </c>
       <c r="W37">
-        <v>0.2265333685803866</v>
+        <v>0.2267907750087092</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1482969484790978</v>
+        <v>0.1441775887991228</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -5816,22 +5816,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1610940593336686</v>
+        <v>0.1629940593336686</v>
       </c>
       <c r="C38">
-        <v>66.8700151864619</v>
+        <v>60.26791638845117</v>
       </c>
       <c r="D38">
-        <v>154.2297751864619</v>
+        <v>151.7293363884512</v>
       </c>
       <c r="E38">
-        <v>147.39376</v>
+        <v>151.49542</v>
       </c>
       <c r="F38">
-        <v>147.65976</v>
+        <v>151.76142</v>
       </c>
       <c r="G38">
         <v>60.3</v>
@@ -5852,37 +5852,37 @@
         <v>5.02</v>
       </c>
       <c r="M38">
-        <v>34.818171408</v>
+        <v>35.785342836</v>
       </c>
       <c r="N38">
-        <v>-29.79817140800001</v>
+        <v>-30.765342836</v>
       </c>
       <c r="O38">
-        <v>-7.896515423120002</v>
+        <v>-8.15281585154</v>
       </c>
       <c r="P38">
-        <v>-21.90165598488</v>
+        <v>-22.61252698446</v>
       </c>
       <c r="Q38">
-        <v>-18.02165598488</v>
+        <v>-18.73252698446</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1241396567664582</v>
+        <v>0.1253831433817988</v>
       </c>
       <c r="T38">
-        <v>1.809229948417048</v>
+        <v>1.837947884106208</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03820706103176755</v>
+        <v>0.0371744377606387</v>
       </c>
       <c r="W38">
-        <v>0.2267907750087092</v>
+        <v>0.2270342675760414</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1441775887991228</v>
+        <v>0.1402808972099574</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -5898,22 +5898,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1629940593336686</v>
+        <v>0.1648940593336686</v>
       </c>
       <c r="C39">
-        <v>60.26791638845117</v>
+        <v>53.74560047369758</v>
       </c>
       <c r="D39">
-        <v>151.7293363884512</v>
+        <v>149.3086804736976</v>
       </c>
       <c r="E39">
-        <v>151.49542</v>
+        <v>155.59708</v>
       </c>
       <c r="F39">
-        <v>151.76142</v>
+        <v>155.86308</v>
       </c>
       <c r="G39">
         <v>60.3</v>
@@ -5934,37 +5934,37 @@
         <v>5.02</v>
       </c>
       <c r="M39">
-        <v>35.785342836</v>
+        <v>36.752514264</v>
       </c>
       <c r="N39">
-        <v>-30.765342836</v>
+        <v>-31.732514264</v>
       </c>
       <c r="O39">
-        <v>-8.15281585154</v>
+        <v>-8.409116279960001</v>
       </c>
       <c r="P39">
-        <v>-22.61252698446</v>
+        <v>-23.32339798404</v>
       </c>
       <c r="Q39">
-        <v>-18.73252698446</v>
+        <v>-19.44339798404</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1253831433817988</v>
+        <v>0.126666742468602</v>
       </c>
       <c r="T39">
-        <v>1.837947884106208</v>
+        <v>1.867592204817598</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0371744377606387</v>
+        <v>0.03619616308272716</v>
       </c>
       <c r="W39">
-        <v>0.2270342675760414</v>
+        <v>0.2272649447450929</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1402808972099574</v>
+        <v>0.1365892946518006</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5980,22 +5980,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1648940593336686</v>
+        <v>0.1667940593336686</v>
       </c>
       <c r="C40">
-        <v>53.74560047369758</v>
+        <v>47.29930889044192</v>
       </c>
       <c r="D40">
-        <v>149.3086804736976</v>
+        <v>146.9640488904419</v>
       </c>
       <c r="E40">
-        <v>155.59708</v>
+        <v>159.69874</v>
       </c>
       <c r="F40">
-        <v>155.86308</v>
+        <v>159.96474</v>
       </c>
       <c r="G40">
         <v>60.3</v>
@@ -6016,37 +6016,37 @@
         <v>5.02</v>
       </c>
       <c r="M40">
-        <v>36.752514264</v>
+        <v>37.71968569200001</v>
       </c>
       <c r="N40">
-        <v>-31.732514264</v>
+        <v>-32.699685692</v>
       </c>
       <c r="O40">
-        <v>-8.409116279960001</v>
+        <v>-8.66541670838</v>
       </c>
       <c r="P40">
-        <v>-23.32339798404</v>
+        <v>-24.03426898362</v>
       </c>
       <c r="Q40">
-        <v>-19.44339798404</v>
+        <v>-20.15426898362</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.126666742468602</v>
+        <v>0.127992426771366</v>
       </c>
       <c r="T40">
-        <v>1.867592204817598</v>
+        <v>1.898208470470346</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03619616308272716</v>
+        <v>0.03526805633701621</v>
       </c>
       <c r="W40">
-        <v>0.2272649447450929</v>
+        <v>0.2274837923157316</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1365892946518006</v>
+        <v>0.1330870050453442</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -6062,22 +6062,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1667940593336686</v>
+        <v>0.1686940593336686</v>
       </c>
       <c r="C41">
-        <v>47.29930889044192</v>
+        <v>40.92551552284201</v>
       </c>
       <c r="D41">
-        <v>146.9640488904419</v>
+        <v>144.691915522842</v>
       </c>
       <c r="E41">
-        <v>159.69874</v>
+        <v>163.8004</v>
       </c>
       <c r="F41">
-        <v>159.96474</v>
+        <v>164.0664</v>
       </c>
       <c r="G41">
         <v>60.3</v>
@@ -6098,37 +6098,37 @@
         <v>5.02</v>
       </c>
       <c r="M41">
-        <v>37.71968569200001</v>
+        <v>38.68685712000001</v>
       </c>
       <c r="N41">
-        <v>-32.699685692</v>
+        <v>-33.66685712</v>
       </c>
       <c r="O41">
-        <v>-8.66541670838</v>
+        <v>-8.921717136800002</v>
       </c>
       <c r="P41">
-        <v>-24.03426898362</v>
+        <v>-24.7451399832</v>
       </c>
       <c r="Q41">
-        <v>-20.15426898362</v>
+        <v>-20.8651399832</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.127992426771366</v>
+        <v>0.1293623005508888</v>
       </c>
       <c r="T41">
-        <v>1.898208470470346</v>
+        <v>1.929845278311518</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03526805633701621</v>
+        <v>0.0343863549285908</v>
       </c>
       <c r="W41">
-        <v>0.2274837923157316</v>
+        <v>0.2276916975078383</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1330870050453442</v>
+        <v>0.1297598299192106</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -6144,22 +6144,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1686940593336686</v>
+        <v>0.1705940593336686</v>
       </c>
       <c r="C42">
-        <v>40.92551552284201</v>
+        <v>34.62090899669084</v>
       </c>
       <c r="D42">
-        <v>144.691915522842</v>
+        <v>142.4889689966909</v>
       </c>
       <c r="E42">
-        <v>163.8004</v>
+        <v>167.90206</v>
       </c>
       <c r="F42">
-        <v>164.0664</v>
+        <v>168.16806</v>
       </c>
       <c r="G42">
         <v>60.3</v>
@@ -6180,37 +6180,37 @@
         <v>5.02</v>
       </c>
       <c r="M42">
-        <v>38.68685712000001</v>
+        <v>39.65402854800001</v>
       </c>
       <c r="N42">
-        <v>-33.66685712</v>
+        <v>-34.634028548</v>
       </c>
       <c r="O42">
-        <v>-8.921717136800002</v>
+        <v>-9.178017565220001</v>
       </c>
       <c r="P42">
-        <v>-24.7451399832</v>
+        <v>-25.45601098278</v>
       </c>
       <c r="Q42">
-        <v>-20.8651399832</v>
+        <v>-21.57601098278</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1293623005508888</v>
+        <v>0.1307786107297174</v>
       </c>
       <c r="T42">
-        <v>1.929845278311518</v>
+        <v>1.962554520316798</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0343863549285908</v>
+        <v>0.03354766334496663</v>
       </c>
       <c r="W42">
-        <v>0.2276916975078383</v>
+        <v>0.2278894609832569</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1297598299192106</v>
+        <v>0.126594956018742</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -6226,22 +6226,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1705940593336686</v>
+        <v>0.1724940593336686</v>
       </c>
       <c r="C43">
-        <v>34.62090899669084</v>
+        <v>28.38237657727689</v>
       </c>
       <c r="D43">
-        <v>142.4889689966909</v>
+        <v>140.3520965772769</v>
       </c>
       <c r="E43">
-        <v>167.90206</v>
+        <v>172.00372</v>
       </c>
       <c r="F43">
-        <v>168.16806</v>
+        <v>172.26972</v>
       </c>
       <c r="G43">
         <v>60.3</v>
@@ -6262,37 +6262,37 @@
         <v>5.02</v>
       </c>
       <c r="M43">
-        <v>39.65402854800001</v>
+        <v>40.621199976</v>
       </c>
       <c r="N43">
-        <v>-34.634028548</v>
+        <v>-35.601199976</v>
       </c>
       <c r="O43">
-        <v>-9.178017565220001</v>
+        <v>-9.434317993639999</v>
       </c>
       <c r="P43">
-        <v>-25.45601098278</v>
+        <v>-26.16688198236</v>
       </c>
       <c r="Q43">
-        <v>-21.57601098278</v>
+        <v>-22.28688198236</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1307786107297174</v>
+        <v>0.1322437591905746</v>
       </c>
       <c r="T43">
-        <v>1.962554520316798</v>
+        <v>1.996391667218812</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03354766334496663</v>
+        <v>0.03274890945580076</v>
       </c>
       <c r="W43">
-        <v>0.2278894609832569</v>
+        <v>0.2280778071503222</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.126594956018742</v>
+        <v>0.1235807903992482</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -6308,22 +6308,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1724940593336686</v>
+        <v>0.1743940593336686</v>
       </c>
       <c r="C44">
-        <v>28.38237657727691</v>
+        <v>22.20698949471483</v>
       </c>
       <c r="D44">
-        <v>140.3520965772769</v>
+        <v>138.2783694947148</v>
       </c>
       <c r="E44">
-        <v>172.00372</v>
+        <v>176.10538</v>
       </c>
       <c r="F44">
-        <v>172.26972</v>
+        <v>176.37138</v>
       </c>
       <c r="G44">
         <v>60.3</v>
@@ -6344,37 +6344,37 @@
         <v>5.02</v>
       </c>
       <c r="M44">
-        <v>40.621199976</v>
+        <v>41.588371404</v>
       </c>
       <c r="N44">
-        <v>-35.601199976</v>
+        <v>-36.568371404</v>
       </c>
       <c r="O44">
-        <v>-9.434317993639999</v>
+        <v>-9.69061842206</v>
       </c>
       <c r="P44">
-        <v>-26.16688198236</v>
+        <v>-26.87775298194</v>
       </c>
       <c r="Q44">
-        <v>-22.28688198236</v>
+        <v>-22.99775298194</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1322437591905746</v>
+        <v>0.1337603163693566</v>
       </c>
       <c r="T44">
-        <v>1.996391667218812</v>
+        <v>2.031416082433177</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03274890945580076</v>
+        <v>0.03198730691031702</v>
       </c>
       <c r="W44">
-        <v>0.2280778071503222</v>
+        <v>0.2282573930305473</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1235807903992482</v>
+        <v>0.1207068185294983</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -6390,22 +6390,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1743940593336686</v>
+        <v>0.1762940593336686</v>
       </c>
       <c r="C45">
-        <v>22.20698949471483</v>
+        <v>16.09198955126058</v>
       </c>
       <c r="D45">
-        <v>138.2783694947148</v>
+        <v>136.2650295512606</v>
       </c>
       <c r="E45">
-        <v>176.10538</v>
+        <v>180.20704</v>
       </c>
       <c r="F45">
-        <v>176.37138</v>
+        <v>180.47304</v>
       </c>
       <c r="G45">
         <v>60.3</v>
@@ -6426,37 +6426,37 @@
         <v>5.02</v>
       </c>
       <c r="M45">
-        <v>41.588371404</v>
+        <v>42.555542832</v>
       </c>
       <c r="N45">
-        <v>-36.568371404</v>
+        <v>-37.535542832</v>
       </c>
       <c r="O45">
-        <v>-9.69061842206</v>
+        <v>-9.946918850479999</v>
       </c>
       <c r="P45">
-        <v>-26.87775298194</v>
+        <v>-27.58862398152</v>
       </c>
       <c r="Q45">
-        <v>-22.99775298194</v>
+        <v>-23.70862398152</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1337603163693566</v>
+        <v>0.1353310363045237</v>
       </c>
       <c r="T45">
-        <v>2.031416082433177</v>
+        <v>2.067691369619484</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03198730691031702</v>
+        <v>0.03126032266235527</v>
       </c>
       <c r="W45">
-        <v>0.2282573930305473</v>
+        <v>0.2284288159162166</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1207068185294983</v>
+        <v>0.1179634817447369</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -6472,22 +6472,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1762940593336686</v>
+        <v>0.1781940593336686</v>
       </c>
       <c r="C46">
-        <v>16.09198955126058</v>
+        <v>10.03477688182483</v>
       </c>
       <c r="D46">
-        <v>136.2650295512606</v>
+        <v>134.3094768818248</v>
       </c>
       <c r="E46">
-        <v>180.20704</v>
+        <v>184.3087</v>
       </c>
       <c r="F46">
-        <v>180.47304</v>
+        <v>184.5747</v>
       </c>
       <c r="G46">
         <v>60.3</v>
@@ -6508,37 +6508,37 @@
         <v>5.02</v>
       </c>
       <c r="M46">
-        <v>42.555542832</v>
+        <v>43.52271426</v>
       </c>
       <c r="N46">
-        <v>-37.535542832</v>
+        <v>-38.50271426</v>
       </c>
       <c r="O46">
-        <v>-9.946918850479999</v>
+        <v>-10.2032192789</v>
       </c>
       <c r="P46">
-        <v>-27.58862398152</v>
+        <v>-28.2994949811</v>
       </c>
       <c r="Q46">
-        <v>-23.70862398152</v>
+        <v>-24.4194949811</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1353310363045237</v>
+        <v>0.1369588733282423</v>
       </c>
       <c r="T46">
-        <v>2.067691369619484</v>
+        <v>2.10528575815802</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03126032266235527</v>
+        <v>0.03056564882541404</v>
       </c>
       <c r="W46">
-        <v>0.2284288159162166</v>
+        <v>0.2285926200069674</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1179634817447369</v>
+        <v>0.1153420710392984</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -6554,22 +6554,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1781940593336686</v>
+        <v>0.1800940593336686</v>
       </c>
       <c r="C47">
-        <v>10.03477688182483</v>
+        <v>4.03289875347545</v>
       </c>
       <c r="D47">
-        <v>134.3094768818248</v>
+        <v>132.4092587534755</v>
       </c>
       <c r="E47">
-        <v>184.3087</v>
+        <v>188.41036</v>
       </c>
       <c r="F47">
-        <v>184.5747</v>
+        <v>188.67636</v>
       </c>
       <c r="G47">
         <v>60.3</v>
@@ -6590,37 +6590,37 @@
         <v>5.02</v>
       </c>
       <c r="M47">
-        <v>43.52271426</v>
+        <v>44.48988568800001</v>
       </c>
       <c r="N47">
-        <v>-38.50271426</v>
+        <v>-39.46988568800001</v>
       </c>
       <c r="O47">
-        <v>-10.2032192789</v>
+        <v>-10.45951970732</v>
       </c>
       <c r="P47">
-        <v>-28.2994949811</v>
+        <v>-29.01036598068</v>
       </c>
       <c r="Q47">
-        <v>-24.4194949811</v>
+        <v>-25.13036598068</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1369588733282423</v>
+        <v>0.1386470006120986</v>
       </c>
       <c r="T47">
-        <v>2.10528575815802</v>
+        <v>2.144272531457243</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03056564882541404</v>
+        <v>0.0299011781987746</v>
       </c>
       <c r="W47">
-        <v>0.2285926200069674</v>
+        <v>0.228749302180729</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1153420710392984</v>
+        <v>0.1128346347123571</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -6636,22 +6636,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1800940593336686</v>
+        <v>0.1819940593336686</v>
       </c>
       <c r="C48">
-        <v>4.03289875347545</v>
+        <v>-1.915960697531801</v>
       </c>
       <c r="D48">
-        <v>132.4092587534755</v>
+        <v>130.5620593024682</v>
       </c>
       <c r="E48">
-        <v>188.41036</v>
+        <v>192.51202</v>
       </c>
       <c r="F48">
-        <v>188.67636</v>
+        <v>192.77802</v>
       </c>
       <c r="G48">
         <v>60.3</v>
@@ -6672,37 +6672,37 @@
         <v>5.02</v>
       </c>
       <c r="M48">
-        <v>44.48988568800001</v>
+        <v>45.457057116</v>
       </c>
       <c r="N48">
-        <v>-39.46988568800001</v>
+        <v>-40.437057116</v>
       </c>
       <c r="O48">
-        <v>-10.45951970732</v>
+        <v>-10.71582013574</v>
       </c>
       <c r="P48">
-        <v>-29.01036598068</v>
+        <v>-29.72123698026</v>
       </c>
       <c r="Q48">
-        <v>-25.13036598068</v>
+        <v>-25.84123698026</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1386470006120986</v>
+        <v>0.1403988308123269</v>
       </c>
       <c r="T48">
-        <v>2.144272531457243</v>
+        <v>2.184730503748888</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0299011781987746</v>
+        <v>0.02926498291794962</v>
       </c>
       <c r="W48">
-        <v>0.228749302180729</v>
+        <v>0.2288993170279475</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1128346347123571</v>
+        <v>0.1104338978035835</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -6718,22 +6718,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1819940593336686</v>
+        <v>0.1838940593336686</v>
       </c>
       <c r="C49">
-        <v>-1.915960697531801</v>
+        <v>-7.813989881489988</v>
       </c>
       <c r="D49">
-        <v>130.5620593024682</v>
+        <v>128.76569011851</v>
       </c>
       <c r="E49">
-        <v>192.51202</v>
+        <v>196.61368</v>
       </c>
       <c r="F49">
-        <v>192.77802</v>
+        <v>196.87968</v>
       </c>
       <c r="G49">
         <v>60.3</v>
@@ -6754,37 +6754,37 @@
         <v>5.02</v>
       </c>
       <c r="M49">
-        <v>45.457057116</v>
+        <v>46.424228544</v>
       </c>
       <c r="N49">
-        <v>-40.437057116</v>
+        <v>-41.404228544</v>
       </c>
       <c r="O49">
-        <v>-10.71582013574</v>
+        <v>-10.97212056416</v>
       </c>
       <c r="P49">
-        <v>-29.72123698026</v>
+        <v>-30.43210797984</v>
       </c>
       <c r="Q49">
-        <v>-25.84123698026</v>
+        <v>-26.55210797984</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1403988308123269</v>
+        <v>0.1422180390971793</v>
       </c>
       <c r="T49">
-        <v>2.184730503748888</v>
+        <v>2.226744551897906</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02926498291794962</v>
+        <v>0.02865529577382567</v>
       </c>
       <c r="W49">
-        <v>0.2288993170279475</v>
+        <v>0.2290430812565319</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1104338978035835</v>
+        <v>0.1081331915993422</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -6800,22 +6800,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1838940593336686</v>
+        <v>0.1857940593336686</v>
       </c>
       <c r="C50">
-        <v>-7.81398988148996</v>
+        <v>-13.6632584042348</v>
       </c>
       <c r="D50">
-        <v>128.76569011851</v>
+        <v>127.0180815957652</v>
       </c>
       <c r="E50">
-        <v>196.61368</v>
+        <v>200.71534</v>
       </c>
       <c r="F50">
-        <v>196.87968</v>
+        <v>200.98134</v>
       </c>
       <c r="G50">
         <v>60.3</v>
@@ -6836,37 +6836,37 @@
         <v>5.02</v>
       </c>
       <c r="M50">
-        <v>46.42422854399999</v>
+        <v>47.391399972</v>
       </c>
       <c r="N50">
-        <v>-41.40422854399999</v>
+        <v>-42.371399972</v>
       </c>
       <c r="O50">
-        <v>-10.97212056416</v>
+        <v>-11.22842099258</v>
       </c>
       <c r="P50">
-        <v>-30.43210797983999</v>
+        <v>-31.14297897942</v>
       </c>
       <c r="Q50">
-        <v>-26.55210797983999</v>
+        <v>-27.26297897942</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1422180390971793</v>
+        <v>0.1441085888833985</v>
       </c>
       <c r="T50">
-        <v>2.226744551897906</v>
+        <v>2.270406209778257</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02865529577382567</v>
+        <v>0.0280704938192578</v>
       </c>
       <c r="W50">
-        <v>0.2290430812565319</v>
+        <v>0.229180977557419</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1081331915993422</v>
+        <v>0.1059263917707842</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -6882,22 +6882,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1857940593336686</v>
+        <v>0.1876940593336686</v>
       </c>
       <c r="C51">
-        <v>-13.6632584042348</v>
+        <v>-19.46572502126483</v>
       </c>
       <c r="D51">
-        <v>127.0180815957652</v>
+        <v>125.3172749787352</v>
       </c>
       <c r="E51">
-        <v>200.71534</v>
+        <v>204.817</v>
       </c>
       <c r="F51">
-        <v>200.98134</v>
+        <v>205.083</v>
       </c>
       <c r="G51">
         <v>60.3</v>
@@ -6918,37 +6918,37 @@
         <v>5.02</v>
       </c>
       <c r="M51">
-        <v>47.391399972</v>
+        <v>48.3585714</v>
       </c>
       <c r="N51">
-        <v>-42.371399972</v>
+        <v>-43.3385714</v>
       </c>
       <c r="O51">
-        <v>-11.22842099258</v>
+        <v>-11.484721421</v>
       </c>
       <c r="P51">
-        <v>-31.14297897942</v>
+        <v>-31.853849979</v>
       </c>
       <c r="Q51">
-        <v>-27.26297897942</v>
+        <v>-27.973849979</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1441085888833985</v>
+        <v>0.1460747606610665</v>
       </c>
       <c r="T51">
-        <v>2.270406209778257</v>
+        <v>2.315814333973822</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0280704938192578</v>
+        <v>0.02750908394287264</v>
       </c>
       <c r="W51">
-        <v>0.229180977557419</v>
+        <v>0.2293133580062706</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1059263917707842</v>
+        <v>0.1038078639353686</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6964,22 +6964,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1876940593336686</v>
+        <v>0.1895940593336686</v>
       </c>
       <c r="C52">
-        <v>-19.46572502126483</v>
+        <v>-25.22324496125782</v>
       </c>
       <c r="D52">
-        <v>125.3172749787352</v>
+        <v>123.6614150387422</v>
       </c>
       <c r="E52">
-        <v>204.817</v>
+        <v>208.91866</v>
       </c>
       <c r="F52">
-        <v>205.083</v>
+        <v>209.18466</v>
       </c>
       <c r="G52">
         <v>60.3</v>
@@ -7000,37 +7000,37 @@
         <v>5.02</v>
       </c>
       <c r="M52">
-        <v>48.3585714</v>
+        <v>49.325742828</v>
       </c>
       <c r="N52">
-        <v>-43.3385714</v>
+        <v>-44.305742828</v>
       </c>
       <c r="O52">
-        <v>-11.484721421</v>
+        <v>-11.74102184942</v>
       </c>
       <c r="P52">
-        <v>-31.853849979</v>
+        <v>-32.56472097858</v>
       </c>
       <c r="Q52">
-        <v>-27.973849979</v>
+        <v>-28.68472097858</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1460747606610665</v>
+        <v>0.1481211843480271</v>
       </c>
       <c r="T52">
-        <v>2.315814333973822</v>
+        <v>2.363075850993696</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02750908394287264</v>
+        <v>0.02696969014007122</v>
       </c>
       <c r="W52">
-        <v>0.2293133580062706</v>
+        <v>0.2294405470649712</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1038078639353686</v>
+        <v>0.1017724156229103</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -7046,22 +7046,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1895940593336686</v>
+        <v>0.1914940593336686</v>
       </c>
       <c r="C53">
-        <v>-25.22324496125782</v>
+        <v>-30.93757667655072</v>
       </c>
       <c r="D53">
-        <v>123.6614150387422</v>
+        <v>122.0487433234493</v>
       </c>
       <c r="E53">
-        <v>208.91866</v>
+        <v>213.02032</v>
       </c>
       <c r="F53">
-        <v>209.18466</v>
+        <v>213.28632</v>
       </c>
       <c r="G53">
         <v>60.3</v>
@@ -7082,37 +7082,37 @@
         <v>5.02</v>
       </c>
       <c r="M53">
-        <v>49.325742828</v>
+        <v>50.292914256</v>
       </c>
       <c r="N53">
-        <v>-44.305742828</v>
+        <v>-45.272914256</v>
       </c>
       <c r="O53">
-        <v>-11.74102184942</v>
+        <v>-11.99732227784</v>
       </c>
       <c r="P53">
-        <v>-32.56472097858</v>
+        <v>-33.27559197816</v>
       </c>
       <c r="Q53">
-        <v>-28.68472097858</v>
+        <v>-29.39559197816</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1481211843480271</v>
+        <v>0.1502528756886109</v>
       </c>
       <c r="T53">
-        <v>2.363075850993696</v>
+        <v>2.412306597889398</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02696969014007122</v>
+        <v>0.02645104225276216</v>
       </c>
       <c r="W53">
-        <v>0.2294405470649712</v>
+        <v>0.2295628442367987</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1017724156229103</v>
+        <v>0.09981525378400813</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -7128,22 +7128,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1914940593336686</v>
+        <v>0.1933940593336686</v>
       </c>
       <c r="C54">
-        <v>-30.93757667655072</v>
+        <v>-36.61038807221979</v>
       </c>
       <c r="D54">
-        <v>122.0487433234493</v>
+        <v>120.4775919277802</v>
       </c>
       <c r="E54">
-        <v>213.02032</v>
+        <v>217.12198</v>
       </c>
       <c r="F54">
-        <v>213.28632</v>
+        <v>217.38798</v>
       </c>
       <c r="G54">
         <v>60.3</v>
@@ -7164,37 +7164,37 @@
         <v>5.02</v>
       </c>
       <c r="M54">
-        <v>50.292914256</v>
+        <v>51.260085684</v>
       </c>
       <c r="N54">
-        <v>-45.272914256</v>
+        <v>-46.240085684</v>
       </c>
       <c r="O54">
-        <v>-11.99732227784</v>
+        <v>-12.25362270626</v>
       </c>
       <c r="P54">
-        <v>-33.27559197816</v>
+        <v>-33.98646297774</v>
       </c>
       <c r="Q54">
-        <v>-29.39559197816</v>
+        <v>-30.10646297774001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1502528756886109</v>
+        <v>0.1524752772990069</v>
       </c>
       <c r="T54">
-        <v>2.412306597889398</v>
+        <v>2.463632270184917</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02645104225276216</v>
+        <v>0.02595196598384212</v>
       </c>
       <c r="W54">
-        <v>0.2295628442367987</v>
+        <v>0.2296805264210101</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.09981525378400813</v>
+        <v>0.09793194710883824</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -7210,22 +7210,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1933940593336686</v>
+        <v>0.1952940593336686</v>
       </c>
       <c r="C55">
-        <v>-36.61038807221979</v>
+        <v>-42.24326226014858</v>
       </c>
       <c r="D55">
-        <v>120.4775919277802</v>
+        <v>118.9463777398514</v>
       </c>
       <c r="E55">
-        <v>217.12198</v>
+        <v>221.22364</v>
       </c>
       <c r="F55">
-        <v>217.38798</v>
+        <v>221.48964</v>
       </c>
       <c r="G55">
         <v>60.3</v>
@@ -7246,37 +7246,37 @@
         <v>5.02</v>
       </c>
       <c r="M55">
-        <v>51.260085684</v>
+        <v>52.227257112</v>
       </c>
       <c r="N55">
-        <v>-46.240085684</v>
+        <v>-47.207257112</v>
       </c>
       <c r="O55">
-        <v>-12.25362270626</v>
+        <v>-12.50992313468</v>
       </c>
       <c r="P55">
-        <v>-33.98646297774</v>
+        <v>-34.69733397732</v>
       </c>
       <c r="Q55">
-        <v>-30.10646297774001</v>
+        <v>-30.81733397732</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1524752772990069</v>
+        <v>0.1547943050663766</v>
       </c>
       <c r="T55">
-        <v>2.463632270184917</v>
+        <v>2.517189493449806</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02595196598384212</v>
+        <v>0.02547137402117837</v>
       </c>
       <c r="W55">
-        <v>0.2296805264210101</v>
+        <v>0.2297938500058062</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.09793194710883824</v>
+        <v>0.09611839253274856</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -7292,22 +7292,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1952940593336686</v>
+        <v>0.1971940593336686</v>
       </c>
       <c r="C56">
-        <v>-42.24326226014858</v>
+        <v>-47.83770287981358</v>
       </c>
       <c r="D56">
-        <v>118.9463777398514</v>
+        <v>117.4535971201864</v>
       </c>
       <c r="E56">
-        <v>221.22364</v>
+        <v>225.3253</v>
       </c>
       <c r="F56">
-        <v>221.48964</v>
+        <v>225.5913</v>
       </c>
       <c r="G56">
         <v>60.3</v>
@@ -7328,37 +7328,37 @@
         <v>5.02</v>
       </c>
       <c r="M56">
-        <v>52.227257112</v>
+        <v>53.19442854</v>
       </c>
       <c r="N56">
-        <v>-47.207257112</v>
+        <v>-48.17442854</v>
       </c>
       <c r="O56">
-        <v>-12.50992313468</v>
+        <v>-12.7662235631</v>
       </c>
       <c r="P56">
-        <v>-34.69733397732</v>
+        <v>-35.4082049769</v>
       </c>
       <c r="Q56">
-        <v>-30.81733397732</v>
+        <v>-31.5282049769</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1547943050663766</v>
+        <v>0.1572164007345183</v>
       </c>
       <c r="T56">
-        <v>2.517189493449806</v>
+        <v>2.573127037748691</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02547137402117837</v>
+        <v>0.02500825812988422</v>
       </c>
       <c r="W56">
-        <v>0.2297938500058062</v>
+        <v>0.2299030527329733</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.09611839253274856</v>
+        <v>0.09437078539578958</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -7374,22 +7374,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1971940593336686</v>
+        <v>0.1990940593336686</v>
       </c>
       <c r="C57">
-        <v>-47.83770287981358</v>
+        <v>-53.39513902337967</v>
       </c>
       <c r="D57">
-        <v>117.4535971201864</v>
+        <v>115.9978209766204</v>
       </c>
       <c r="E57">
-        <v>225.3253</v>
+        <v>229.42696</v>
       </c>
       <c r="F57">
-        <v>225.5913</v>
+        <v>229.69296</v>
       </c>
       <c r="G57">
         <v>60.3</v>
@@ -7410,37 +7410,37 @@
         <v>5.02</v>
       </c>
       <c r="M57">
-        <v>53.19442854</v>
+        <v>54.16159996800001</v>
       </c>
       <c r="N57">
-        <v>-48.17442854</v>
+        <v>-49.14159996800001</v>
       </c>
       <c r="O57">
-        <v>-12.7662235631</v>
+        <v>-13.02252399152</v>
       </c>
       <c r="P57">
-        <v>-35.4082049769</v>
+        <v>-36.11907597648</v>
       </c>
       <c r="Q57">
-        <v>-31.5282049769</v>
+        <v>-32.23907597648</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1572164007345183</v>
+        <v>0.1597485916603028</v>
       </c>
       <c r="T57">
-        <v>2.573127037748691</v>
+        <v>2.631607197697525</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02500825812988422</v>
+        <v>0.02456168209185057</v>
       </c>
       <c r="W57">
-        <v>0.2299030527329733</v>
+        <v>0.2300083553627416</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.09437078539578958</v>
+        <v>0.09268559279943611</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -7456,22 +7456,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1990940593336686</v>
+        <v>0.2009940593336686</v>
       </c>
       <c r="C58">
-        <v>-53.39513902337967</v>
+        <v>-58.91692979901543</v>
       </c>
       <c r="D58">
-        <v>115.9978209766204</v>
+        <v>114.5776902009846</v>
       </c>
       <c r="E58">
-        <v>229.42696</v>
+        <v>233.52862</v>
       </c>
       <c r="F58">
-        <v>229.69296</v>
+        <v>233.79462</v>
       </c>
       <c r="G58">
         <v>60.3</v>
@@ -7492,37 +7492,37 @@
         <v>5.02</v>
       </c>
       <c r="M58">
-        <v>54.16159996800001</v>
+        <v>55.12877139600001</v>
       </c>
       <c r="N58">
-        <v>-49.14159996800001</v>
+        <v>-50.10877139600001</v>
       </c>
       <c r="O58">
-        <v>-13.02252399152</v>
+        <v>-13.27882441994</v>
       </c>
       <c r="P58">
-        <v>-36.11907597648</v>
+        <v>-36.82994697606001</v>
       </c>
       <c r="Q58">
-        <v>-32.23907597648</v>
+        <v>-32.94994697606</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1597485916603028</v>
+        <v>0.1623985589082169</v>
       </c>
       <c r="T58">
-        <v>2.631607197697525</v>
+        <v>2.69280736508584</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02456168209185057</v>
+        <v>0.02413077538848477</v>
       </c>
       <c r="W58">
-        <v>0.2300083553627416</v>
+        <v>0.2301099631633953</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.09268559279943611</v>
+        <v>0.09105952976786713</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -7538,22 +7538,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2009940593336686</v>
+        <v>0.2028940593336686</v>
       </c>
       <c r="C59">
-        <v>-58.91692979901543</v>
+        <v>-64.40436856305817</v>
       </c>
       <c r="D59">
-        <v>114.5776902009846</v>
+        <v>113.1919114369418</v>
       </c>
       <c r="E59">
-        <v>233.52862</v>
+        <v>237.63028</v>
       </c>
       <c r="F59">
-        <v>233.79462</v>
+        <v>237.89628</v>
       </c>
       <c r="G59">
         <v>60.3</v>
@@ -7574,37 +7574,37 @@
         <v>5.02</v>
       </c>
       <c r="M59">
-        <v>55.12877139600001</v>
+        <v>56.09594282400001</v>
       </c>
       <c r="N59">
-        <v>-50.10877139600001</v>
+        <v>-51.075942824</v>
       </c>
       <c r="O59">
-        <v>-13.27882441994</v>
+        <v>-13.53512484836</v>
       </c>
       <c r="P59">
-        <v>-36.82994697606001</v>
+        <v>-37.54081797564</v>
       </c>
       <c r="Q59">
-        <v>-32.94994697606</v>
+        <v>-33.66081797564</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1623985589082169</v>
+        <v>0.1651747150726982</v>
       </c>
       <c r="T59">
-        <v>2.69280736508584</v>
+        <v>2.756921826159312</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02413077538848477</v>
+        <v>0.02371472753695917</v>
       </c>
       <c r="W59">
-        <v>0.2301099631633953</v>
+        <v>0.2302080672467851</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.09105952976786713</v>
+        <v>0.08948953787531766</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -7620,22 +7620,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2028940593336686</v>
+        <v>0.2047940593336685</v>
       </c>
       <c r="C60">
-        <v>-64.40436856305811</v>
+        <v>-69.85868684872929</v>
       </c>
       <c r="D60">
-        <v>113.1919114369419</v>
+        <v>111.8392531512707</v>
       </c>
       <c r="E60">
-        <v>237.63028</v>
+        <v>241.73194</v>
       </c>
       <c r="F60">
-        <v>237.89628</v>
+        <v>241.99794</v>
       </c>
       <c r="G60">
         <v>60.3</v>
@@ -7656,37 +7656,37 @@
         <v>5.02</v>
       </c>
       <c r="M60">
-        <v>56.095942824</v>
+        <v>57.063114252</v>
       </c>
       <c r="N60">
-        <v>-51.07594282399999</v>
+        <v>-52.043114252</v>
       </c>
       <c r="O60">
-        <v>-13.53512484836</v>
+        <v>-13.79142527678</v>
       </c>
       <c r="P60">
-        <v>-37.54081797564</v>
+        <v>-38.25168897521999</v>
       </c>
       <c r="Q60">
-        <v>-33.66081797563999</v>
+        <v>-34.37168897521999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1651747150726982</v>
+        <v>0.1680862934891054</v>
       </c>
       <c r="T60">
-        <v>2.756921826159312</v>
+        <v>2.824163821919294</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02371472753695917</v>
+        <v>0.02331278300243444</v>
       </c>
       <c r="W60">
-        <v>0.2302080672467851</v>
+        <v>0.230302845768026</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.08948953787531766</v>
+        <v>0.0879727660469225</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -7702,22 +7702,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2047940593336685</v>
+        <v>0.2066940593336686</v>
       </c>
       <c r="C61">
-        <v>-69.85868684872929</v>
+        <v>-75.28105801648437</v>
       </c>
       <c r="D61">
-        <v>111.8392531512707</v>
+        <v>110.5185419835156</v>
       </c>
       <c r="E61">
-        <v>241.73194</v>
+        <v>245.8336</v>
       </c>
       <c r="F61">
-        <v>241.99794</v>
+        <v>246.0996</v>
       </c>
       <c r="G61">
         <v>60.3</v>
@@ -7738,37 +7738,37 @@
         <v>5.02</v>
       </c>
       <c r="M61">
-        <v>57.063114252</v>
+        <v>58.03028568</v>
       </c>
       <c r="N61">
-        <v>-52.043114252</v>
+        <v>-53.01028568</v>
       </c>
       <c r="O61">
-        <v>-13.79142527678</v>
+        <v>-14.0477257052</v>
       </c>
       <c r="P61">
-        <v>-38.25168897521999</v>
+        <v>-38.96255997479999</v>
       </c>
       <c r="Q61">
-        <v>-34.37168897521999</v>
+        <v>-35.08255997479999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1680862934891054</v>
+        <v>0.1711434508263331</v>
       </c>
       <c r="T61">
-        <v>2.824163821919294</v>
+        <v>2.894767917467277</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02331278300243444</v>
+        <v>0.02292423661906054</v>
       </c>
       <c r="W61">
-        <v>0.230302845768026</v>
+        <v>0.2303944650052255</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.0879727660469225</v>
+        <v>0.08650655327947376</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -7784,22 +7784,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2066940593336686</v>
+        <v>0.2085940593336685</v>
       </c>
       <c r="C62">
-        <v>-75.28105801648437</v>
+        <v>-80.67260064873867</v>
       </c>
       <c r="D62">
-        <v>110.5185419835156</v>
+        <v>109.2286593512613</v>
       </c>
       <c r="E62">
-        <v>245.8336</v>
+        <v>249.93526</v>
       </c>
       <c r="F62">
-        <v>246.0996</v>
+        <v>250.20126</v>
       </c>
       <c r="G62">
         <v>60.3</v>
@@ -7820,37 +7820,37 @@
         <v>5.02</v>
       </c>
       <c r="M62">
-        <v>58.03028568</v>
+        <v>58.997457108</v>
       </c>
       <c r="N62">
-        <v>-53.01028568</v>
+        <v>-53.977457108</v>
       </c>
       <c r="O62">
-        <v>-14.0477257052</v>
+        <v>-14.30402613362</v>
       </c>
       <c r="P62">
-        <v>-38.96255997479999</v>
+        <v>-39.67343097438</v>
       </c>
       <c r="Q62">
-        <v>-35.08255997479999</v>
+        <v>-35.79343097437999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1711434508263331</v>
+        <v>0.1743573854629058</v>
       </c>
       <c r="T62">
-        <v>2.894767917467277</v>
+        <v>2.968992735863874</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02292423661906054</v>
+        <v>0.02254842946137102</v>
       </c>
       <c r="W62">
-        <v>0.2303944650052255</v>
+        <v>0.2304830803330087</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.08650655327947376</v>
+        <v>0.0850884130617775</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -7866,22 +7866,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2085940593336685</v>
+        <v>0.2104940593336686</v>
       </c>
       <c r="C63">
-        <v>-80.67260064873867</v>
+        <v>-86.03438170961397</v>
       </c>
       <c r="D63">
-        <v>109.2286593512613</v>
+        <v>107.968538290386</v>
       </c>
       <c r="E63">
-        <v>249.93526</v>
+        <v>254.03692</v>
       </c>
       <c r="F63">
-        <v>250.20126</v>
+        <v>254.30292</v>
       </c>
       <c r="G63">
         <v>60.3</v>
@@ -7902,37 +7902,37 @@
         <v>5.02</v>
       </c>
       <c r="M63">
-        <v>58.997457108</v>
+        <v>59.964628536</v>
       </c>
       <c r="N63">
-        <v>-53.977457108</v>
+        <v>-54.944628536</v>
       </c>
       <c r="O63">
-        <v>-14.30402613362</v>
+        <v>-14.56032656204</v>
       </c>
       <c r="P63">
-        <v>-39.67343097438</v>
+        <v>-40.38430197395999</v>
       </c>
       <c r="Q63">
-        <v>-35.79343097437999</v>
+        <v>-36.50430197395999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1743573854629058</v>
+        <v>0.1777404745540349</v>
       </c>
       <c r="T63">
-        <v>2.968992735863874</v>
+        <v>3.047124123649766</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02254842946137102</v>
+        <v>0.02218474511521987</v>
       </c>
       <c r="W63">
-        <v>0.2304830803330087</v>
+        <v>0.2305688371018312</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.0850884130617775</v>
+        <v>0.08371601930271655</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7948,22 +7948,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2104940593336686</v>
+        <v>0.2123940593336686</v>
       </c>
       <c r="C64">
-        <v>-86.03438170961397</v>
+        <v>-91.36741948846299</v>
       </c>
       <c r="D64">
-        <v>107.968538290386</v>
+        <v>106.737160511537</v>
       </c>
       <c r="E64">
-        <v>254.03692</v>
+        <v>258.13858</v>
       </c>
       <c r="F64">
-        <v>254.30292</v>
+        <v>258.40458</v>
       </c>
       <c r="G64">
         <v>60.3</v>
@@ -7984,37 +7984,37 @@
         <v>5.02</v>
       </c>
       <c r="M64">
-        <v>59.964628536</v>
+        <v>60.93179996400001</v>
       </c>
       <c r="N64">
-        <v>-54.944628536</v>
+        <v>-55.911799964</v>
       </c>
       <c r="O64">
-        <v>-14.56032656204</v>
+        <v>-14.81662699046</v>
       </c>
       <c r="P64">
-        <v>-40.38430197395999</v>
+        <v>-41.09517297354</v>
       </c>
       <c r="Q64">
-        <v>-36.50430197395999</v>
+        <v>-37.21517297354</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1777404745540349</v>
+        <v>0.1813064333257655</v>
       </c>
       <c r="T64">
-        <v>3.047124123649766</v>
+        <v>3.129478829694354</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02218474511521987</v>
+        <v>0.02183260630386718</v>
       </c>
       <c r="W64">
-        <v>0.2305688371018312</v>
+        <v>0.2306518714335481</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.08371601930271655</v>
+        <v>0.08238719359949875</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -8030,22 +8030,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2123940593336686</v>
+        <v>0.2142940593336686</v>
       </c>
       <c r="C65">
-        <v>-91.36741948846299</v>
+        <v>-96.6726863442413</v>
       </c>
       <c r="D65">
-        <v>106.737160511537</v>
+        <v>105.5335536557587</v>
       </c>
       <c r="E65">
-        <v>258.13858</v>
+        <v>262.24024</v>
       </c>
       <c r="F65">
-        <v>258.40458</v>
+        <v>262.50624</v>
       </c>
       <c r="G65">
         <v>60.3</v>
@@ -8066,37 +8066,37 @@
         <v>5.02</v>
       </c>
       <c r="M65">
-        <v>60.93179996400001</v>
+        <v>61.898971392</v>
       </c>
       <c r="N65">
-        <v>-55.911799964</v>
+        <v>-56.878971392</v>
       </c>
       <c r="O65">
-        <v>-14.81662699046</v>
+        <v>-15.07292741888</v>
       </c>
       <c r="P65">
-        <v>-41.09517297354</v>
+        <v>-41.80604397312</v>
       </c>
       <c r="Q65">
-        <v>-37.21517297354</v>
+        <v>-37.92604397312</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1813064333257655</v>
+        <v>0.1850705009181479</v>
       </c>
       <c r="T65">
-        <v>3.129478829694354</v>
+        <v>3.216408797185864</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02183260630386718</v>
+        <v>0.02149147183036925</v>
       </c>
       <c r="W65">
-        <v>0.2306518714335481</v>
+        <v>0.2307323109423989</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.08238719359949875</v>
+        <v>0.08109989369950665</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -8112,22 +8112,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2142940593336686</v>
+        <v>0.2161940593336686</v>
       </c>
       <c r="C66">
-        <v>-96.6726863442413</v>
+        <v>-101.95111126627</v>
       </c>
       <c r="D66">
-        <v>105.5335536557587</v>
+        <v>104.35678873373</v>
       </c>
       <c r="E66">
-        <v>262.24024</v>
+        <v>266.3419</v>
       </c>
       <c r="F66">
-        <v>262.50624</v>
+        <v>266.6079</v>
       </c>
       <c r="G66">
         <v>60.3</v>
@@ -8148,37 +8148,37 @@
         <v>5.02</v>
       </c>
       <c r="M66">
-        <v>61.898971392</v>
+        <v>62.86614282000001</v>
       </c>
       <c r="N66">
-        <v>-56.878971392</v>
+        <v>-57.84614282</v>
       </c>
       <c r="O66">
-        <v>-15.07292741888</v>
+        <v>-15.3292278473</v>
       </c>
       <c r="P66">
-        <v>-41.80604397312</v>
+        <v>-42.5169149727</v>
       </c>
       <c r="Q66">
-        <v>-37.92604397312</v>
+        <v>-38.6369149727</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1850705009181479</v>
+        <v>0.1890496580872379</v>
       </c>
       <c r="T66">
-        <v>3.216408797185864</v>
+        <v>3.308306191391174</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02149147183036925</v>
+        <v>0.02116083380220972</v>
       </c>
       <c r="W66">
-        <v>0.2307323109423989</v>
+        <v>0.230810275389439</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.08109989369950665</v>
+        <v>0.07985220302720653</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -8194,22 +8194,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2161940593336686</v>
+        <v>0.2180940593336686</v>
       </c>
       <c r="C67">
-        <v>-101.95111126627</v>
+        <v>-107.2035822655634</v>
       </c>
       <c r="D67">
-        <v>104.35678873373</v>
+        <v>103.2059777344366</v>
       </c>
       <c r="E67">
-        <v>266.3419</v>
+        <v>270.44356</v>
       </c>
       <c r="F67">
-        <v>266.6079</v>
+        <v>270.70956</v>
       </c>
       <c r="G67">
         <v>60.3</v>
@@ -8230,37 +8230,37 @@
         <v>5.02</v>
       </c>
       <c r="M67">
-        <v>62.86614282000001</v>
+        <v>63.83331424800001</v>
       </c>
       <c r="N67">
-        <v>-57.84614282</v>
+        <v>-58.813314248</v>
       </c>
       <c r="O67">
-        <v>-15.3292278473</v>
+        <v>-15.58552827572</v>
       </c>
       <c r="P67">
-        <v>-42.5169149727</v>
+        <v>-43.22778597228</v>
       </c>
       <c r="Q67">
-        <v>-38.6369149727</v>
+        <v>-39.34778597228</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1890496580872379</v>
+        <v>0.1932628833250978</v>
       </c>
       <c r="T67">
-        <v>3.308306191391174</v>
+        <v>3.405609314667385</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02116083380220972</v>
+        <v>0.02084021510823685</v>
       </c>
       <c r="W67">
-        <v>0.230810275389439</v>
+        <v>0.2308858772774778</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.07985220302720653</v>
+        <v>0.07864232116315795</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -8276,22 +8276,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2180940593336686</v>
+        <v>0.2199940593336686</v>
       </c>
       <c r="C68">
-        <v>-107.2035822655634</v>
+        <v>-112.4309486096575</v>
       </c>
       <c r="D68">
-        <v>103.2059777344366</v>
+        <v>102.0802713903425</v>
       </c>
       <c r="E68">
-        <v>270.44356</v>
+        <v>274.54522</v>
       </c>
       <c r="F68">
-        <v>270.70956</v>
+        <v>274.81122</v>
       </c>
       <c r="G68">
         <v>60.3</v>
@@ -8312,37 +8312,37 @@
         <v>5.02</v>
       </c>
       <c r="M68">
-        <v>63.83331424800001</v>
+        <v>64.80048567599999</v>
       </c>
       <c r="N68">
-        <v>-58.813314248</v>
+        <v>-59.78048567599999</v>
       </c>
       <c r="O68">
-        <v>-15.58552827572</v>
+        <v>-15.84182870414</v>
       </c>
       <c r="P68">
-        <v>-43.22778597228</v>
+        <v>-43.93865697185999</v>
       </c>
       <c r="Q68">
-        <v>-39.34778597228</v>
+        <v>-40.05865697185999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1932628833250978</v>
+        <v>0.1977314555470705</v>
       </c>
       <c r="T68">
-        <v>3.405609314667385</v>
+        <v>3.508809596930033</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02084021510823685</v>
+        <v>0.02052916712154675</v>
       </c>
       <c r="W68">
-        <v>0.2308858772774778</v>
+        <v>0.2309592223927393</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.07864232116315795</v>
+        <v>0.0774685551756481</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -8358,22 +8358,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2199940593336686</v>
+        <v>0.2218940593336686</v>
       </c>
       <c r="C69">
-        <v>-112.4309486096575</v>
+        <v>-117.634022912761</v>
       </c>
       <c r="D69">
-        <v>102.0802713903425</v>
+        <v>100.978857087239</v>
       </c>
       <c r="E69">
-        <v>274.54522</v>
+        <v>278.64688</v>
       </c>
       <c r="F69">
-        <v>274.81122</v>
+        <v>278.91288</v>
       </c>
       <c r="G69">
         <v>60.3</v>
@@ -8394,37 +8394,37 @@
         <v>5.02</v>
       </c>
       <c r="M69">
-        <v>64.80048567599999</v>
+        <v>65.76765710400001</v>
       </c>
       <c r="N69">
-        <v>-59.78048567599999</v>
+        <v>-60.74765710400001</v>
       </c>
       <c r="O69">
-        <v>-15.84182870414</v>
+        <v>-16.09812913256</v>
       </c>
       <c r="P69">
-        <v>-43.93865697185999</v>
+        <v>-44.64952797144001</v>
       </c>
       <c r="Q69">
-        <v>-40.05865697185999</v>
+        <v>-40.76952797144001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1977314555470705</v>
+        <v>0.2024793135329164</v>
       </c>
       <c r="T69">
-        <v>3.508809596930033</v>
+        <v>3.618459896834097</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02052916712154675</v>
+        <v>0.02022726760505341</v>
       </c>
       <c r="W69">
-        <v>0.2309592223927393</v>
+        <v>0.2310304102987284</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.0774685551756481</v>
+        <v>0.07632931171718271</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -8440,22 +8440,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2218940593336686</v>
+        <v>0.2237940593336686</v>
       </c>
       <c r="C70">
-        <v>-117.634022912761</v>
+        <v>-122.8135830920366</v>
       </c>
       <c r="D70">
-        <v>100.978857087239</v>
+        <v>99.90095690796343</v>
       </c>
       <c r="E70">
-        <v>278.64688</v>
+        <v>282.74854</v>
       </c>
       <c r="F70">
-        <v>278.91288</v>
+        <v>283.01454</v>
       </c>
       <c r="G70">
         <v>60.3</v>
@@ -8476,37 +8476,37 @@
         <v>5.02</v>
       </c>
       <c r="M70">
-        <v>65.76765710400001</v>
+        <v>66.73482853200001</v>
       </c>
       <c r="N70">
-        <v>-60.74765710400001</v>
+        <v>-61.71482853200001</v>
       </c>
       <c r="O70">
-        <v>-16.09812913256</v>
+        <v>-16.35442956098</v>
       </c>
       <c r="P70">
-        <v>-44.64952797144001</v>
+        <v>-45.36039897102</v>
       </c>
       <c r="Q70">
-        <v>-40.76952797144001</v>
+        <v>-41.48039897102</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2024793135329164</v>
+        <v>0.2075334849372041</v>
       </c>
       <c r="T70">
-        <v>3.618459896834097</v>
+        <v>3.735184409635197</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02022726760505341</v>
+        <v>0.01993411879918307</v>
       </c>
       <c r="W70">
-        <v>0.2310304102987284</v>
+        <v>0.2310995347871526</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.07632931171718271</v>
+        <v>0.075223089808238</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -8522,22 +8522,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2237940593336686</v>
+        <v>0.2256940593336686</v>
       </c>
       <c r="C71">
-        <v>-122.8135830920366</v>
+        <v>-127.9703741999131</v>
       </c>
       <c r="D71">
-        <v>99.90095690796343</v>
+        <v>98.84582580008694</v>
       </c>
       <c r="E71">
-        <v>282.74854</v>
+        <v>286.8502</v>
       </c>
       <c r="F71">
-        <v>283.01454</v>
+        <v>287.1162</v>
       </c>
       <c r="G71">
         <v>60.3</v>
@@ -8558,37 +8558,37 @@
         <v>5.02</v>
       </c>
       <c r="M71">
-        <v>66.73482853200001</v>
+        <v>67.70199996000001</v>
       </c>
       <c r="N71">
-        <v>-61.71482853200001</v>
+        <v>-62.68199996000001</v>
       </c>
       <c r="O71">
-        <v>-16.35442956098</v>
+        <v>-16.6107299894</v>
       </c>
       <c r="P71">
-        <v>-45.36039897102</v>
+        <v>-46.0712699706</v>
       </c>
       <c r="Q71">
-        <v>-41.48039897102</v>
+        <v>-42.1912699706</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2075334849372041</v>
+        <v>0.2129246011017775</v>
       </c>
       <c r="T71">
-        <v>3.735184409635197</v>
+        <v>3.859690556623037</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01993411879918307</v>
+        <v>0.01964934567348046</v>
       </c>
       <c r="W71">
-        <v>0.2310995347871526</v>
+        <v>0.2311666842901933</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.075223089808238</v>
+        <v>0.07414847423954896</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -8604,22 +8604,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2256940593336686</v>
+        <v>0.2275940593336686</v>
       </c>
       <c r="C72">
-        <v>-127.9703741999131</v>
+        <v>-133.1051101414952</v>
       </c>
       <c r="D72">
-        <v>98.84582580008694</v>
+        <v>97.81274985850482</v>
       </c>
       <c r="E72">
-        <v>286.8502</v>
+        <v>290.95186</v>
       </c>
       <c r="F72">
-        <v>287.1162</v>
+        <v>291.21786</v>
       </c>
       <c r="G72">
         <v>60.3</v>
@@ -8640,37 +8640,37 @@
         <v>5.02</v>
       </c>
       <c r="M72">
-        <v>67.70199996000001</v>
+        <v>68.66917138800001</v>
       </c>
       <c r="N72">
-        <v>-62.68199996000001</v>
+        <v>-63.64917138800001</v>
       </c>
       <c r="O72">
-        <v>-16.6107299894</v>
+        <v>-16.86703041782</v>
       </c>
       <c r="P72">
-        <v>-46.0712699706</v>
+        <v>-46.78214097018</v>
       </c>
       <c r="Q72">
-        <v>-42.1912699706</v>
+        <v>-42.90214097018</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2129246011017775</v>
+        <v>0.2186875183811492</v>
       </c>
       <c r="T72">
-        <v>3.859690556623037</v>
+        <v>3.992783334437625</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01964934567348046</v>
+        <v>0.01937259432596665</v>
       </c>
       <c r="W72">
-        <v>0.2311666842901933</v>
+        <v>0.2312319422579371</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.07414847423954896</v>
+        <v>0.07310412953194967</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -8686,22 +8686,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2275940593336686</v>
+        <v>0.2294940593336686</v>
       </c>
       <c r="C73">
-        <v>-133.1051101414951</v>
+        <v>-138.218475285392</v>
       </c>
       <c r="D73">
-        <v>97.81274985850486</v>
+        <v>96.80104471460801</v>
       </c>
       <c r="E73">
-        <v>290.95186</v>
+        <v>295.05352</v>
       </c>
       <c r="F73">
-        <v>291.21786</v>
+        <v>295.31952</v>
       </c>
       <c r="G73">
         <v>60.3</v>
@@ -8722,37 +8722,37 @@
         <v>5.02</v>
       </c>
       <c r="M73">
-        <v>68.669171388</v>
+        <v>69.63634281600001</v>
       </c>
       <c r="N73">
-        <v>-63.64917138799999</v>
+        <v>-64.61634281600001</v>
       </c>
       <c r="O73">
-        <v>-16.86703041782</v>
+        <v>-17.12333084624001</v>
       </c>
       <c r="P73">
-        <v>-46.78214097018</v>
+        <v>-47.49301196976</v>
       </c>
       <c r="Q73">
-        <v>-42.90214097017999</v>
+        <v>-43.61301196976</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2186875183811491</v>
+        <v>0.2248620726090473</v>
       </c>
       <c r="T73">
-        <v>3.992783334437624</v>
+        <v>4.135382739238968</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01937259432596665</v>
+        <v>0.01910353051588378</v>
       </c>
       <c r="W73">
-        <v>0.2312319422579371</v>
+        <v>0.2312953875043546</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.07310412953194967</v>
+        <v>0.0720887943995614</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -8768,22 +8768,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2294940593336686</v>
+        <v>0.2313940593336686</v>
       </c>
       <c r="C74">
-        <v>-138.218475285392</v>
+        <v>-143.3111259756009</v>
       </c>
       <c r="D74">
-        <v>96.80104471460801</v>
+        <v>95.81005402439905</v>
       </c>
       <c r="E74">
-        <v>295.05352</v>
+        <v>299.15518</v>
       </c>
       <c r="F74">
-        <v>295.31952</v>
+        <v>299.42118</v>
       </c>
       <c r="G74">
         <v>60.3</v>
@@ -8804,37 +8804,37 @@
         <v>5.02</v>
       </c>
       <c r="M74">
-        <v>69.63634281600001</v>
+        <v>70.603514244</v>
       </c>
       <c r="N74">
-        <v>-64.61634281600001</v>
+        <v>-65.583514244</v>
       </c>
       <c r="O74">
-        <v>-17.12333084624001</v>
+        <v>-17.37963127466</v>
       </c>
       <c r="P74">
-        <v>-47.49301196976</v>
+        <v>-48.20388296934</v>
       </c>
       <c r="Q74">
-        <v>-43.61301196976</v>
+        <v>-44.32388296934</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2248620726090473</v>
+        <v>0.2314940012241972</v>
       </c>
       <c r="T74">
-        <v>4.135382739238968</v>
+        <v>4.288545062914484</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01910353051588378</v>
+        <v>0.01884183831703606</v>
       </c>
       <c r="W74">
-        <v>0.2312953875043546</v>
+        <v>0.2313570945248429</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.0720887943995614</v>
+        <v>0.07110127666806054</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -8850,22 +8850,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2313940593336686</v>
+        <v>0.2332940593336686</v>
       </c>
       <c r="C75">
-        <v>-143.3111259756009</v>
+        <v>-148.3836919514666</v>
       </c>
       <c r="D75">
-        <v>95.81005402439905</v>
+        <v>94.83914804853342</v>
       </c>
       <c r="E75">
-        <v>299.15518</v>
+        <v>303.25684</v>
       </c>
       <c r="F75">
-        <v>299.42118</v>
+        <v>303.52284</v>
       </c>
       <c r="G75">
         <v>60.3</v>
@@ -8886,37 +8886,37 @@
         <v>5.02</v>
       </c>
       <c r="M75">
-        <v>70.603514244</v>
+        <v>71.570685672</v>
       </c>
       <c r="N75">
-        <v>-65.583514244</v>
+        <v>-66.550685672</v>
       </c>
       <c r="O75">
-        <v>-17.37963127466</v>
+        <v>-17.63593170308</v>
       </c>
       <c r="P75">
-        <v>-48.20388296934</v>
+        <v>-48.91475396892</v>
       </c>
       <c r="Q75">
-        <v>-44.32388296934</v>
+        <v>-45.03475396891999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2314940012241972</v>
+        <v>0.2386360781943587</v>
       </c>
       <c r="T75">
-        <v>4.288545062914484</v>
+        <v>4.453489103795811</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01884183831703606</v>
+        <v>0.01858721888031935</v>
       </c>
       <c r="W75">
-        <v>0.2313570945248429</v>
+        <v>0.2314171337880207</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.07110127666806054</v>
+        <v>0.07014044860497859</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8932,22 +8932,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2332940593336686</v>
+        <v>0.2351940593336685</v>
       </c>
       <c r="C76">
-        <v>-148.3836919514666</v>
+        <v>-153.4367776821689</v>
       </c>
       <c r="D76">
-        <v>94.83914804853342</v>
+        <v>93.88772231783115</v>
       </c>
       <c r="E76">
-        <v>303.25684</v>
+        <v>307.3585</v>
       </c>
       <c r="F76">
-        <v>303.52284</v>
+        <v>307.6245</v>
       </c>
       <c r="G76">
         <v>60.3</v>
@@ -8968,37 +8968,37 @@
         <v>5.02</v>
       </c>
       <c r="M76">
-        <v>71.570685672</v>
+        <v>72.53785710000001</v>
       </c>
       <c r="N76">
-        <v>-66.550685672</v>
+        <v>-67.51785710000001</v>
       </c>
       <c r="O76">
-        <v>-17.63593170308</v>
+        <v>-17.89223213150001</v>
       </c>
       <c r="P76">
-        <v>-48.91475396892</v>
+        <v>-49.62562496850001</v>
       </c>
       <c r="Q76">
-        <v>-45.03475396891999</v>
+        <v>-45.7456249685</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2386360781943587</v>
+        <v>0.246349521322133</v>
       </c>
       <c r="T76">
-        <v>4.453489103795811</v>
+        <v>4.631628667947644</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01858721888031935</v>
+        <v>0.01833938929524843</v>
       </c>
       <c r="W76">
-        <v>0.2314171337880207</v>
+        <v>0.2314755720041804</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07014044860497859</v>
+        <v>0.06920524262357886</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -9014,22 +9014,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2351940593336685</v>
+        <v>0.2370940593336686</v>
       </c>
       <c r="C77">
-        <v>-153.4367776821689</v>
+        <v>-158.4709636216845</v>
       </c>
       <c r="D77">
-        <v>93.88772231783115</v>
+        <v>92.95519637831551</v>
       </c>
       <c r="E77">
-        <v>307.3585</v>
+        <v>311.46016</v>
       </c>
       <c r="F77">
-        <v>307.6245</v>
+        <v>311.72616</v>
       </c>
       <c r="G77">
         <v>60.3</v>
@@ -9050,37 +9050,37 @@
         <v>5.02</v>
       </c>
       <c r="M77">
-        <v>72.53785710000001</v>
+        <v>73.505028528</v>
       </c>
       <c r="N77">
-        <v>-67.51785710000001</v>
+        <v>-68.485028528</v>
       </c>
       <c r="O77">
-        <v>-17.89223213150001</v>
+        <v>-18.14853255992</v>
       </c>
       <c r="P77">
-        <v>-49.62562496850001</v>
+        <v>-50.33649596808</v>
       </c>
       <c r="Q77">
-        <v>-45.7456249685</v>
+        <v>-46.45649596808</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.246349521322133</v>
+        <v>0.2547057513772218</v>
       </c>
       <c r="T77">
-        <v>4.631628667947644</v>
+        <v>4.824613195778795</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01833938929524843</v>
+        <v>0.01809808154136358</v>
       </c>
       <c r="W77">
-        <v>0.2314755720041804</v>
+        <v>0.2315324723725465</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.06920524262357886</v>
+        <v>0.06829464732590029</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -9096,22 +9096,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2370940593336686</v>
+        <v>0.2389940593336686</v>
       </c>
       <c r="C78">
-        <v>-158.4709636216845</v>
+        <v>-163.4868073896945</v>
       </c>
       <c r="D78">
-        <v>92.95519637831551</v>
+        <v>92.04101261030557</v>
       </c>
       <c r="E78">
-        <v>311.46016</v>
+        <v>315.56182</v>
       </c>
       <c r="F78">
-        <v>311.72616</v>
+        <v>315.82782</v>
       </c>
       <c r="G78">
         <v>60.3</v>
@@ -9132,37 +9132,37 @@
         <v>5.02</v>
       </c>
       <c r="M78">
-        <v>73.505028528</v>
+        <v>74.47219995600001</v>
       </c>
       <c r="N78">
-        <v>-68.485028528</v>
+        <v>-69.45219995600002</v>
       </c>
       <c r="O78">
-        <v>-18.14853255992</v>
+        <v>-18.40483298834</v>
       </c>
       <c r="P78">
-        <v>-50.33649596808</v>
+        <v>-51.04736696766001</v>
       </c>
       <c r="Q78">
-        <v>-46.45649596808</v>
+        <v>-47.16736696766001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2547057513772218</v>
+        <v>0.2637886101327533</v>
       </c>
       <c r="T78">
-        <v>4.824613195778795</v>
+        <v>5.034378986899613</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01809808154136358</v>
+        <v>0.01786304152134587</v>
       </c>
       <c r="W78">
-        <v>0.2315324723725465</v>
+        <v>0.2315878948092666</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.06829464732590029</v>
+        <v>0.0674077038541353</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -9178,22 +9178,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2389940593336686</v>
+        <v>0.2408940593336686</v>
       </c>
       <c r="C79">
-        <v>-163.4868073896945</v>
+        <v>-168.4848448834883</v>
       </c>
       <c r="D79">
-        <v>92.04101261030557</v>
+        <v>91.14463511651172</v>
       </c>
       <c r="E79">
-        <v>315.56182</v>
+        <v>319.66348</v>
       </c>
       <c r="F79">
-        <v>315.82782</v>
+        <v>319.92948</v>
       </c>
       <c r="G79">
         <v>60.3</v>
@@ -9214,37 +9214,37 @@
         <v>5.02</v>
       </c>
       <c r="M79">
-        <v>74.47219995600001</v>
+        <v>75.43937138400001</v>
       </c>
       <c r="N79">
-        <v>-69.45219995600002</v>
+        <v>-70.41937138400002</v>
       </c>
       <c r="O79">
-        <v>-18.40483298834</v>
+        <v>-18.66113341676001</v>
       </c>
       <c r="P79">
-        <v>-51.04736696766001</v>
+        <v>-51.75823796724001</v>
       </c>
       <c r="Q79">
-        <v>-47.16736696766001</v>
+        <v>-47.87823796724</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2637886101327533</v>
+        <v>0.2736971833206057</v>
       </c>
       <c r="T79">
-        <v>5.034378986899613</v>
+        <v>5.26321439539505</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01786304152134587</v>
+        <v>0.0176340281685081</v>
       </c>
       <c r="W79">
-        <v>0.2315878948092666</v>
+        <v>0.2316418961578658</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0674077038541353</v>
+        <v>0.06654350252267205</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -9260,22 +9260,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2408940593336686</v>
+        <v>0.2427940593336686</v>
       </c>
       <c r="C80">
-        <v>-168.4848448834883</v>
+        <v>-173.4655913255218</v>
       </c>
       <c r="D80">
-        <v>91.14463511651172</v>
+        <v>90.26554867447817</v>
       </c>
       <c r="E80">
-        <v>319.66348</v>
+        <v>323.76514</v>
       </c>
       <c r="F80">
-        <v>319.92948</v>
+        <v>324.03114</v>
       </c>
       <c r="G80">
         <v>60.3</v>
@@ -9296,37 +9296,37 @@
         <v>5.02</v>
       </c>
       <c r="M80">
-        <v>75.43937138400001</v>
+        <v>76.406542812</v>
       </c>
       <c r="N80">
-        <v>-70.41937138400002</v>
+        <v>-71.386542812</v>
       </c>
       <c r="O80">
-        <v>-18.66113341676001</v>
+        <v>-18.91743384518</v>
       </c>
       <c r="P80">
-        <v>-51.75823796724001</v>
+        <v>-52.46910896682</v>
       </c>
       <c r="Q80">
-        <v>-47.87823796724</v>
+        <v>-48.58910896682</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2736971833206057</v>
+        <v>0.2845494301453964</v>
       </c>
       <c r="T80">
-        <v>5.26321439539505</v>
+        <v>5.513843652318624</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0176340281685081</v>
+        <v>0.01741081262207129</v>
       </c>
       <c r="W80">
-        <v>0.2316418961578658</v>
+        <v>0.2316945303837156</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.06654350252267205</v>
+        <v>0.06570117970592937</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -9342,22 +9342,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2427940593336686</v>
+        <v>0.2446940593336686</v>
       </c>
       <c r="C81">
-        <v>-173.4655913255218</v>
+        <v>-178.4295422509325</v>
       </c>
       <c r="D81">
-        <v>90.26554867447817</v>
+        <v>89.40325774906754</v>
       </c>
       <c r="E81">
-        <v>323.76514</v>
+        <v>327.8668</v>
       </c>
       <c r="F81">
-        <v>324.03114</v>
+        <v>328.1328</v>
       </c>
       <c r="G81">
         <v>60.3</v>
@@ -9378,37 +9378,37 @@
         <v>5.02</v>
       </c>
       <c r="M81">
-        <v>76.406542812</v>
+        <v>77.37371424000001</v>
       </c>
       <c r="N81">
-        <v>-71.386542812</v>
+        <v>-72.35371424000002</v>
       </c>
       <c r="O81">
-        <v>-18.91743384518</v>
+        <v>-19.1737342736</v>
       </c>
       <c r="P81">
-        <v>-52.46910896682</v>
+        <v>-53.17997996640001</v>
       </c>
       <c r="Q81">
-        <v>-48.58910896682</v>
+        <v>-49.29997996640001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2845494301453964</v>
+        <v>0.2964869016526663</v>
       </c>
       <c r="T81">
-        <v>5.513843652318624</v>
+        <v>5.789535834934556</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01741081262207129</v>
+        <v>0.0171931774642954</v>
       </c>
       <c r="W81">
-        <v>0.2316945303837156</v>
+        <v>0.2317458487539192</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.06570117970592937</v>
+        <v>0.06487991495960521</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -9424,22 +9424,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2446940593336686</v>
+        <v>0.2465940593336686</v>
       </c>
       <c r="C82">
-        <v>-178.4295422509325</v>
+        <v>-183.3771744389888</v>
       </c>
       <c r="D82">
-        <v>89.40325774906754</v>
+        <v>88.5572855610112</v>
       </c>
       <c r="E82">
-        <v>327.8668</v>
+        <v>331.96846</v>
       </c>
       <c r="F82">
-        <v>328.1328</v>
+        <v>332.23446</v>
       </c>
       <c r="G82">
         <v>60.3</v>
@@ -9460,37 +9460,37 @@
         <v>5.02</v>
       </c>
       <c r="M82">
-        <v>77.37371424000001</v>
+        <v>78.34088566800001</v>
       </c>
       <c r="N82">
-        <v>-72.35371424000002</v>
+        <v>-73.32088566800002</v>
       </c>
       <c r="O82">
-        <v>-19.1737342736</v>
+        <v>-19.43003470202001</v>
       </c>
       <c r="P82">
-        <v>-53.17997996640001</v>
+        <v>-53.89085096598001</v>
       </c>
       <c r="Q82">
-        <v>-49.29997996640001</v>
+        <v>-50.01085096598</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2964869016526663</v>
+        <v>0.3096809491080698</v>
       </c>
       <c r="T82">
-        <v>5.789535834934556</v>
+        <v>6.094248247299532</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0171931774642954</v>
+        <v>0.01698091601411891</v>
       </c>
       <c r="W82">
-        <v>0.2317458487539192</v>
+        <v>0.2317959000038708</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.06487991495960521</v>
+        <v>0.0640789283551656</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -9506,22 +9506,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2465940593336686</v>
+        <v>0.2484940593336686</v>
       </c>
       <c r="C83">
-        <v>-183.3771744389888</v>
+        <v>-188.3089467921533</v>
       </c>
       <c r="D83">
-        <v>88.5572855610112</v>
+        <v>87.72717320784676</v>
       </c>
       <c r="E83">
-        <v>331.96846</v>
+        <v>336.07012</v>
       </c>
       <c r="F83">
-        <v>332.23446</v>
+        <v>336.3361200000001</v>
       </c>
       <c r="G83">
         <v>60.3</v>
@@ -9542,37 +9542,37 @@
         <v>5.02</v>
       </c>
       <c r="M83">
-        <v>78.34088566800001</v>
+        <v>79.30805709600001</v>
       </c>
       <c r="N83">
-        <v>-73.32088566800002</v>
+        <v>-74.28805709600002</v>
       </c>
       <c r="O83">
-        <v>-19.43003470202001</v>
+        <v>-19.68633513044001</v>
       </c>
       <c r="P83">
-        <v>-53.89085096598001</v>
+        <v>-54.60172196556001</v>
       </c>
       <c r="Q83">
-        <v>-50.01085096598</v>
+        <v>-50.72172196556001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3096809491080698</v>
+        <v>0.3243410018362959</v>
       </c>
       <c r="T83">
-        <v>6.094248247299532</v>
+        <v>6.43281759437173</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01698091601411891</v>
+        <v>0.01677383167248332</v>
       </c>
       <c r="W83">
-        <v>0.2317959000038708</v>
+        <v>0.2318447304916284</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.0640789283551656</v>
+        <v>0.06329747800937091</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -9588,22 +9588,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2484940593336686</v>
+        <v>0.2503940593336686</v>
       </c>
       <c r="C84">
-        <v>-188.3089467921533</v>
+        <v>-193.2253011661628</v>
       </c>
       <c r="D84">
-        <v>87.72717320784676</v>
+        <v>86.91247883383723</v>
       </c>
       <c r="E84">
-        <v>336.07012</v>
+        <v>340.17178</v>
       </c>
       <c r="F84">
-        <v>336.3361200000001</v>
+        <v>340.43778</v>
       </c>
       <c r="G84">
         <v>60.3</v>
@@ -9624,37 +9624,37 @@
         <v>5.02</v>
       </c>
       <c r="M84">
-        <v>79.30805709600001</v>
+        <v>80.27522852400001</v>
       </c>
       <c r="N84">
-        <v>-74.28805709600002</v>
+        <v>-75.25522852400002</v>
       </c>
       <c r="O84">
-        <v>-19.68633513044001</v>
+        <v>-19.94263555886</v>
       </c>
       <c r="P84">
-        <v>-54.60172196556001</v>
+        <v>-55.31259296514001</v>
       </c>
       <c r="Q84">
-        <v>-50.72172196556001</v>
+        <v>-51.43259296514001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3243410018362959</v>
+        <v>0.3407257666501957</v>
       </c>
       <c r="T84">
-        <v>6.43281759437173</v>
+        <v>6.811218629334773</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01677383167248332</v>
+        <v>0.01657173731498352</v>
       </c>
       <c r="W84">
-        <v>0.2318447304916284</v>
+        <v>0.2318923843411269</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.06329747800937091</v>
+        <v>0.06253485779239054</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -9670,22 +9670,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2503940593336686</v>
+        <v>0.2522940593336686</v>
       </c>
       <c r="C85">
-        <v>-193.2253011661628</v>
+        <v>-198.1266631542837</v>
       </c>
       <c r="D85">
-        <v>86.91247883383723</v>
+        <v>86.11277684571633</v>
       </c>
       <c r="E85">
-        <v>340.17178</v>
+        <v>344.27344</v>
       </c>
       <c r="F85">
-        <v>340.43778</v>
+        <v>344.53944</v>
       </c>
       <c r="G85">
         <v>60.3</v>
@@ -9706,37 +9706,37 @@
         <v>5.02</v>
       </c>
       <c r="M85">
-        <v>80.27522852400001</v>
+        <v>81.242399952</v>
       </c>
       <c r="N85">
-        <v>-75.25522852400002</v>
+        <v>-76.222399952</v>
       </c>
       <c r="O85">
-        <v>-19.94263555886</v>
+        <v>-20.19893598728</v>
       </c>
       <c r="P85">
-        <v>-55.31259296514001</v>
+        <v>-56.02346396472</v>
       </c>
       <c r="Q85">
-        <v>-51.43259296514001</v>
+        <v>-52.14346396472</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3407257666501957</v>
+        <v>0.359158627065833</v>
       </c>
       <c r="T85">
-        <v>6.811218629334773</v>
+        <v>7.236919793668198</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01657173731498352</v>
+        <v>0.01637445472790038</v>
       </c>
       <c r="W85">
-        <v>0.2318923843411269</v>
+        <v>0.2319389035751611</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06253485779239054</v>
+        <v>0.06179039519962404</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -9752,22 +9752,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2522940593336686</v>
+        <v>0.2541940593336686</v>
       </c>
       <c r="C86">
-        <v>-198.1266631542836</v>
+        <v>-203.013442828664</v>
       </c>
       <c r="D86">
-        <v>86.11277684571633</v>
+        <v>85.32765717133594</v>
       </c>
       <c r="E86">
-        <v>344.2734399999999</v>
+        <v>348.3751</v>
       </c>
       <c r="F86">
-        <v>344.53944</v>
+        <v>348.6411</v>
       </c>
       <c r="G86">
         <v>60.3</v>
@@ -9788,37 +9788,37 @@
         <v>5.02</v>
       </c>
       <c r="M86">
-        <v>81.242399952</v>
+        <v>82.20957138</v>
       </c>
       <c r="N86">
-        <v>-76.222399952</v>
+        <v>-77.18957138</v>
       </c>
       <c r="O86">
-        <v>-20.19893598728</v>
+        <v>-20.4552364157</v>
       </c>
       <c r="P86">
-        <v>-56.02346396472</v>
+        <v>-56.7343349643</v>
       </c>
       <c r="Q86">
-        <v>-52.14346396472</v>
+        <v>-52.8543349643</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3591586270658328</v>
+        <v>0.380049202203555</v>
       </c>
       <c r="T86">
-        <v>7.236919793668193</v>
+        <v>7.719381113246072</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01637445472790038</v>
+        <v>0.01618181408404273</v>
       </c>
       <c r="W86">
-        <v>0.2319389035751611</v>
+        <v>0.2319843282389827</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06179039519962404</v>
+        <v>0.06106344937374608</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -9834,22 +9834,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2541940593336686</v>
+        <v>0.2560940593336686</v>
       </c>
       <c r="C87">
-        <v>-203.013442828664</v>
+        <v>-207.8860354414979</v>
       </c>
       <c r="D87">
-        <v>85.32765717133594</v>
+        <v>84.5567245585021</v>
       </c>
       <c r="E87">
-        <v>348.3751</v>
+        <v>352.47676</v>
       </c>
       <c r="F87">
-        <v>348.6411</v>
+        <v>352.74276</v>
       </c>
       <c r="G87">
         <v>60.3</v>
@@ -9870,37 +9870,37 @@
         <v>5.02</v>
       </c>
       <c r="M87">
-        <v>82.20957138</v>
+        <v>83.176742808</v>
       </c>
       <c r="N87">
-        <v>-77.18957138</v>
+        <v>-78.156742808</v>
       </c>
       <c r="O87">
-        <v>-20.4552364157</v>
+        <v>-20.71153684412</v>
       </c>
       <c r="P87">
-        <v>-56.7343349643</v>
+        <v>-57.44520596388</v>
       </c>
       <c r="Q87">
-        <v>-52.8543349643</v>
+        <v>-53.56520596388</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.380049202203555</v>
+        <v>0.4039241452180947</v>
       </c>
       <c r="T87">
-        <v>7.719381113246072</v>
+        <v>8.270765478477935</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01618181408404273</v>
+        <v>0.01599365345515851</v>
       </c>
       <c r="W87">
-        <v>0.2319843282389827</v>
+        <v>0.2320286965152736</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06106344937374608</v>
+        <v>0.06035340926474908</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -9916,22 +9916,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2560940593336686</v>
+        <v>0.2579940593336686</v>
       </c>
       <c r="C88">
-        <v>-207.8860354414979</v>
+        <v>-212.7448220885193</v>
       </c>
       <c r="D88">
-        <v>84.5567245585021</v>
+        <v>83.79959791148072</v>
       </c>
       <c r="E88">
-        <v>352.47676</v>
+        <v>356.57842</v>
       </c>
       <c r="F88">
-        <v>352.74276</v>
+        <v>356.84442</v>
       </c>
       <c r="G88">
         <v>60.3</v>
@@ -9952,37 +9952,37 @@
         <v>5.02</v>
       </c>
       <c r="M88">
-        <v>83.176742808</v>
+        <v>84.143914236</v>
       </c>
       <c r="N88">
-        <v>-78.156742808</v>
+        <v>-79.123914236</v>
       </c>
       <c r="O88">
-        <v>-20.71153684412</v>
+        <v>-20.96783727254</v>
       </c>
       <c r="P88">
-        <v>-57.44520596388</v>
+        <v>-58.15607696346</v>
       </c>
       <c r="Q88">
-        <v>-53.56520596388</v>
+        <v>-54.27607696346</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4039241452180947</v>
+        <v>0.4314721563887173</v>
       </c>
       <c r="T88">
-        <v>8.270765478477935</v>
+        <v>8.906978207591623</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01599365345515851</v>
+        <v>0.01580981835797278</v>
       </c>
       <c r="W88">
-        <v>0.2320286965152736</v>
+        <v>0.23207204483119</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06035340926474908</v>
+        <v>0.05965969191687837</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9998,22 +9998,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2579940593336686</v>
+        <v>0.2598940593336686</v>
       </c>
       <c r="C89">
-        <v>-212.7448220885193</v>
+        <v>-217.5901703371674</v>
       </c>
       <c r="D89">
-        <v>83.79959791148072</v>
+        <v>83.05590966283263</v>
       </c>
       <c r="E89">
-        <v>356.57842</v>
+        <v>360.68008</v>
       </c>
       <c r="F89">
-        <v>356.84442</v>
+        <v>360.94608</v>
       </c>
       <c r="G89">
         <v>60.3</v>
@@ -10034,37 +10034,37 @@
         <v>5.02</v>
       </c>
       <c r="M89">
-        <v>84.143914236</v>
+        <v>85.111085664</v>
       </c>
       <c r="N89">
-        <v>-79.123914236</v>
+        <v>-80.091085664</v>
       </c>
       <c r="O89">
-        <v>-20.96783727254</v>
+        <v>-21.22413770096</v>
       </c>
       <c r="P89">
-        <v>-58.15607696346</v>
+        <v>-58.86694796304</v>
       </c>
       <c r="Q89">
-        <v>-54.27607696346</v>
+        <v>-54.98694796304</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4314721563887173</v>
+        <v>0.4636115027544437</v>
       </c>
       <c r="T89">
-        <v>8.906978207591623</v>
+        <v>9.64922639155759</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01580981835797278</v>
+        <v>0.01563016133117764</v>
       </c>
       <c r="W89">
-        <v>0.23207204483119</v>
+        <v>0.2321144079581083</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.05965969191687837</v>
+        <v>0.0589817408723684</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -10080,22 +10080,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2598940593336686</v>
+        <v>0.2617940593336686</v>
       </c>
       <c r="C90">
-        <v>-217.5901703371674</v>
+        <v>-222.4224348215972</v>
       </c>
       <c r="D90">
-        <v>83.05590966283263</v>
+        <v>82.32530517840281</v>
       </c>
       <c r="E90">
-        <v>360.68008</v>
+        <v>364.78174</v>
       </c>
       <c r="F90">
-        <v>360.94608</v>
+        <v>365.04774</v>
       </c>
       <c r="G90">
         <v>60.3</v>
@@ -10116,37 +10116,37 @@
         <v>5.02</v>
       </c>
       <c r="M90">
-        <v>85.111085664</v>
+        <v>86.078257092</v>
       </c>
       <c r="N90">
-        <v>-80.091085664</v>
+        <v>-81.05825709200001</v>
       </c>
       <c r="O90">
-        <v>-21.22413770096</v>
+        <v>-21.48043812938</v>
       </c>
       <c r="P90">
-        <v>-58.86694796304</v>
+        <v>-59.57781896262</v>
       </c>
       <c r="Q90">
-        <v>-54.98694796304</v>
+        <v>-55.69781896262</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4636115027544437</v>
+        <v>0.5015943666412114</v>
       </c>
       <c r="T90">
-        <v>9.64922639155759</v>
+        <v>10.5264287907901</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01563016133117764</v>
+        <v>0.01545454154093969</v>
       </c>
       <c r="W90">
-        <v>0.2321144079581083</v>
+        <v>0.2321558191046464</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.0589817408723684</v>
+        <v>0.05831902468279127</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -10162,22 +10162,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2617940593336686</v>
+        <v>0.2636940593336686</v>
       </c>
       <c r="C91">
-        <v>-222.4224348215972</v>
+        <v>-227.2419578065602</v>
       </c>
       <c r="D91">
-        <v>82.32530517840281</v>
+        <v>81.60744219343985</v>
       </c>
       <c r="E91">
-        <v>364.78174</v>
+        <v>368.8834</v>
       </c>
       <c r="F91">
-        <v>365.04774</v>
+        <v>369.1494</v>
       </c>
       <c r="G91">
         <v>60.3</v>
@@ -10198,37 +10198,37 @@
         <v>5.02</v>
       </c>
       <c r="M91">
-        <v>86.078257092</v>
+        <v>87.04542852</v>
       </c>
       <c r="N91">
-        <v>-81.05825709200001</v>
+        <v>-82.02542852000001</v>
       </c>
       <c r="O91">
-        <v>-21.48043812938</v>
+        <v>-21.7367385578</v>
       </c>
       <c r="P91">
-        <v>-59.57781896262</v>
+        <v>-60.2886899622</v>
       </c>
       <c r="Q91">
-        <v>-55.69781896262</v>
+        <v>-56.4086899622</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5015943666412114</v>
+        <v>0.5471738033053325</v>
       </c>
       <c r="T91">
-        <v>10.5264287907901</v>
+        <v>11.57907166986911</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01545454154093969</v>
+        <v>0.01528282441270702</v>
       </c>
       <c r="W91">
-        <v>0.2321558191046464</v>
+        <v>0.2321963100034837</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.05831902468279127</v>
+        <v>0.05767103551964914</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -10244,22 +10244,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2636940593336686</v>
+        <v>0.2655940593336686</v>
       </c>
       <c r="C92">
-        <v>-227.2419578065602</v>
+        <v>-232.0490697220378</v>
       </c>
       <c r="D92">
-        <v>81.60744219343985</v>
+        <v>80.90199027796224</v>
       </c>
       <c r="E92">
-        <v>368.8834</v>
+        <v>372.98506</v>
       </c>
       <c r="F92">
-        <v>369.1494</v>
+        <v>373.25106</v>
       </c>
       <c r="G92">
         <v>60.3</v>
@@ -10280,37 +10280,37 @@
         <v>5.02</v>
       </c>
       <c r="M92">
-        <v>87.04542852</v>
+        <v>88.012599948</v>
       </c>
       <c r="N92">
-        <v>-82.02542852000001</v>
+        <v>-82.99259994800001</v>
       </c>
       <c r="O92">
-        <v>-21.7367385578</v>
+        <v>-21.99303898622</v>
       </c>
       <c r="P92">
-        <v>-60.2886899622</v>
+        <v>-60.99956096178001</v>
       </c>
       <c r="Q92">
-        <v>-56.4086899622</v>
+        <v>-57.11956096178</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5471738033053325</v>
+        <v>0.6028820036725918</v>
       </c>
       <c r="T92">
-        <v>11.57907166986911</v>
+        <v>12.86563518874346</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01528282441270702</v>
+        <v>0.01511488128729266</v>
       </c>
       <c r="W92">
-        <v>0.2321963100034837</v>
+        <v>0.2322359109924564</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.05767103551964914</v>
+        <v>0.05703728787657603</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -10326,22 +10326,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2655940593336686</v>
+        <v>0.2674940593336686</v>
       </c>
       <c r="C93">
-        <v>-232.0490697220378</v>
+        <v>-236.8440896703835</v>
       </c>
       <c r="D93">
-        <v>80.90199027796224</v>
+        <v>80.20863032961658</v>
       </c>
       <c r="E93">
-        <v>372.98506</v>
+        <v>377.08672</v>
       </c>
       <c r="F93">
-        <v>373.25106</v>
+        <v>377.35272</v>
       </c>
       <c r="G93">
         <v>60.3</v>
@@ -10362,37 +10362,37 @@
         <v>5.02</v>
       </c>
       <c r="M93">
-        <v>88.012599948</v>
+        <v>88.97977137600002</v>
       </c>
       <c r="N93">
-        <v>-82.99259994800001</v>
+        <v>-83.95977137600002</v>
       </c>
       <c r="O93">
-        <v>-21.99303898622</v>
+        <v>-22.24933941464</v>
       </c>
       <c r="P93">
-        <v>-60.99956096178001</v>
+        <v>-61.71043196136002</v>
       </c>
       <c r="Q93">
-        <v>-57.11956096178</v>
+        <v>-57.83043196136001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6028820036725918</v>
+        <v>0.672517254131666</v>
       </c>
       <c r="T93">
-        <v>12.86563518874346</v>
+        <v>14.4738395873364</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01511488128729266</v>
+        <v>0.0149505890993873</v>
       </c>
       <c r="W93">
-        <v>0.2322359109924564</v>
+        <v>0.2322746510903645</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.05703728787657603</v>
+        <v>0.0564173173561785</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -10408,22 +10408,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2674940593336686</v>
+        <v>0.2693940593336686</v>
       </c>
       <c r="C94">
-        <v>-236.8440896703835</v>
+        <v>-241.6273259076074</v>
       </c>
       <c r="D94">
-        <v>80.20863032961658</v>
+        <v>79.52705409239263</v>
       </c>
       <c r="E94">
-        <v>377.08672</v>
+        <v>381.18838</v>
       </c>
       <c r="F94">
-        <v>377.35272</v>
+        <v>381.45438</v>
       </c>
       <c r="G94">
         <v>60.3</v>
@@ -10444,37 +10444,37 @@
         <v>5.02</v>
       </c>
       <c r="M94">
-        <v>88.97977137600002</v>
+        <v>89.946942804</v>
       </c>
       <c r="N94">
-        <v>-83.95977137600002</v>
+        <v>-84.92694280400001</v>
       </c>
       <c r="O94">
-        <v>-22.24933941464</v>
+        <v>-22.50563984306</v>
       </c>
       <c r="P94">
-        <v>-61.71043196136002</v>
+        <v>-62.42130296094</v>
       </c>
       <c r="Q94">
-        <v>-57.83043196136001</v>
+        <v>-58.54130296094</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.672517254131666</v>
+        <v>0.7620482904361897</v>
       </c>
       <c r="T94">
-        <v>14.4738395873364</v>
+        <v>16.54153095695588</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0149505890993873</v>
+        <v>0.01478983007681325</v>
       </c>
       <c r="W94">
-        <v>0.2322746510903645</v>
+        <v>0.2323125580678874</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.0564173173561785</v>
+        <v>0.05581067953514429</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -10490,22 +10490,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2693940593336686</v>
+        <v>0.2712940593336686</v>
       </c>
       <c r="C95">
-        <v>-241.6273259076074</v>
+        <v>-246.3990763003301</v>
       </c>
       <c r="D95">
-        <v>79.52705409239263</v>
+        <v>78.85696369966988</v>
       </c>
       <c r="E95">
-        <v>381.18838</v>
+        <v>385.29004</v>
       </c>
       <c r="F95">
-        <v>381.45438</v>
+        <v>385.55604</v>
       </c>
       <c r="G95">
         <v>60.3</v>
@@ -10526,37 +10526,37 @@
         <v>5.02</v>
       </c>
       <c r="M95">
-        <v>89.946942804</v>
+        <v>90.914114232</v>
       </c>
       <c r="N95">
-        <v>-84.92694280400001</v>
+        <v>-85.89411423200001</v>
       </c>
       <c r="O95">
-        <v>-22.50563984306</v>
+        <v>-22.76194027148</v>
       </c>
       <c r="P95">
-        <v>-62.42130296094</v>
+        <v>-63.13217396052001</v>
       </c>
       <c r="Q95">
-        <v>-58.54130296094</v>
+        <v>-59.25217396052</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7620482904361897</v>
+        <v>0.8814230055088882</v>
       </c>
       <c r="T95">
-        <v>16.54153095695588</v>
+        <v>19.2984527831152</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01478983007681325</v>
+        <v>0.01463249145897481</v>
       </c>
       <c r="W95">
-        <v>0.2323125580678874</v>
+        <v>0.2323496585139737</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.05581067953514429</v>
+        <v>0.05521694890179163</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -10572,22 +10572,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2712940593336686</v>
+        <v>0.2731940593336686</v>
       </c>
       <c r="C96">
-        <v>-246.3990763003301</v>
+        <v>-251.1596287598272</v>
       </c>
       <c r="D96">
-        <v>78.85696369966988</v>
+        <v>78.19807124017287</v>
       </c>
       <c r="E96">
-        <v>385.29004</v>
+        <v>389.3917</v>
       </c>
       <c r="F96">
-        <v>385.55604</v>
+        <v>389.6577</v>
       </c>
       <c r="G96">
         <v>60.3</v>
@@ -10608,37 +10608,37 @@
         <v>5.02</v>
       </c>
       <c r="M96">
-        <v>90.914114232</v>
+        <v>91.88128566000002</v>
       </c>
       <c r="N96">
-        <v>-85.89411423200001</v>
+        <v>-86.86128566000002</v>
       </c>
       <c r="O96">
-        <v>-22.76194027148</v>
+        <v>-23.01824069990001</v>
       </c>
       <c r="P96">
-        <v>-63.13217396052001</v>
+        <v>-63.84304496010002</v>
       </c>
       <c r="Q96">
-        <v>-59.25217396052</v>
+        <v>-59.96304496010001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8814230055088882</v>
+        <v>1.048547606610667</v>
       </c>
       <c r="T96">
-        <v>19.2984527831152</v>
+        <v>23.15814333973826</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01463249145897481</v>
+        <v>0.01447846523309086</v>
       </c>
       <c r="W96">
-        <v>0.2323496585139737</v>
+        <v>0.2323859778980372</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.05521694890179163</v>
+        <v>0.05463571786072019</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -10654,22 +10654,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2731940593336686</v>
+        <v>0.2750940593336685</v>
       </c>
       <c r="C97">
-        <v>-251.1596287598272</v>
+        <v>-255.9092616544939</v>
       </c>
       <c r="D97">
-        <v>78.19807124017287</v>
+        <v>77.55009834550614</v>
       </c>
       <c r="E97">
-        <v>389.3917</v>
+        <v>393.49336</v>
       </c>
       <c r="F97">
-        <v>389.6577</v>
+        <v>393.75936</v>
       </c>
       <c r="G97">
         <v>60.3</v>
@@ -10690,37 +10690,37 @@
         <v>5.02</v>
       </c>
       <c r="M97">
-        <v>91.88128566000002</v>
+        <v>92.848457088</v>
       </c>
       <c r="N97">
-        <v>-86.86128566000002</v>
+        <v>-87.82845708800001</v>
       </c>
       <c r="O97">
-        <v>-23.01824069990001</v>
+        <v>-23.27454112832</v>
       </c>
       <c r="P97">
-        <v>-63.84304496010002</v>
+        <v>-64.55391595968001</v>
       </c>
       <c r="Q97">
-        <v>-59.96304496010001</v>
+        <v>-60.67391595968001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.048547606610667</v>
+        <v>1.299234508263333</v>
       </c>
       <c r="T97">
-        <v>23.15814333973826</v>
+        <v>28.94767917467282</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01447846523309086</v>
+        <v>0.01432764788691283</v>
       </c>
       <c r="W97">
-        <v>0.2323859778980372</v>
+        <v>0.2324215406282659</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.05463571786072019</v>
+        <v>0.05406659579967099</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -10736,22 +10736,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2750940593336685</v>
+        <v>0.2769940593336686</v>
       </c>
       <c r="C98">
-        <v>-255.9092616544938</v>
+        <v>-260.6482442019725</v>
       </c>
       <c r="D98">
-        <v>77.55009834550614</v>
+        <v>76.91277579802745</v>
       </c>
       <c r="E98">
-        <v>393.4933599999999</v>
+        <v>397.59502</v>
       </c>
       <c r="F98">
-        <v>393.75936</v>
+        <v>397.86102</v>
       </c>
       <c r="G98">
         <v>60.3</v>
@@ -10772,37 +10772,37 @@
         <v>5.02</v>
       </c>
       <c r="M98">
-        <v>92.84845708799999</v>
+        <v>93.815628516</v>
       </c>
       <c r="N98">
-        <v>-87.82845708799999</v>
+        <v>-88.79562851600001</v>
       </c>
       <c r="O98">
-        <v>-23.27454112832</v>
+        <v>-23.53084155674</v>
       </c>
       <c r="P98">
-        <v>-64.55391595968</v>
+        <v>-65.26478695926001</v>
       </c>
       <c r="Q98">
-        <v>-60.67391595968</v>
+        <v>-61.38478695926</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.29923450826333</v>
+        <v>1.717046011017773</v>
       </c>
       <c r="T98">
-        <v>28.94767917467275</v>
+        <v>38.59690556623033</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01432764788691284</v>
+        <v>0.01417994017673847</v>
       </c>
       <c r="W98">
-        <v>0.2324215406282659</v>
+        <v>0.2324563701063251</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.05406659579967099</v>
+        <v>0.05350920821410743</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -10818,22 +10818,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2769940593336686</v>
+        <v>0.2788940593336686</v>
       </c>
       <c r="C99">
-        <v>-260.6482442019725</v>
+        <v>-265.3768368421007</v>
       </c>
       <c r="D99">
-        <v>76.91277579802745</v>
+        <v>76.28584315789931</v>
       </c>
       <c r="E99">
-        <v>397.59502</v>
+        <v>401.69668</v>
       </c>
       <c r="F99">
-        <v>397.86102</v>
+        <v>401.96268</v>
       </c>
       <c r="G99">
         <v>60.3</v>
@@ -10854,37 +10854,37 @@
         <v>5.02</v>
       </c>
       <c r="M99">
-        <v>93.815628516</v>
+        <v>94.782799944</v>
       </c>
       <c r="N99">
-        <v>-88.79562851600001</v>
+        <v>-89.76279994400001</v>
       </c>
       <c r="O99">
-        <v>-23.53084155674</v>
+        <v>-23.78714198516</v>
       </c>
       <c r="P99">
-        <v>-65.26478695926001</v>
+        <v>-65.97565795884</v>
       </c>
       <c r="Q99">
-        <v>-61.38478695926</v>
+        <v>-62.09565795884</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.717046011017773</v>
+        <v>2.55266901652666</v>
       </c>
       <c r="T99">
-        <v>38.59690556623033</v>
+        <v>57.8953583493455</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01417994017673847</v>
+        <v>0.0140352469096289</v>
       </c>
       <c r="W99">
-        <v>0.2324563701063251</v>
+        <v>0.2324904887787095</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.05350920821410743</v>
+        <v>0.052963195885392</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -10900,22 +10900,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2788940593336686</v>
+        <v>0.2807940593336686</v>
       </c>
       <c r="C100">
-        <v>-265.3768368421007</v>
+        <v>-270.095291591768</v>
       </c>
       <c r="D100">
-        <v>76.28584315789931</v>
+        <v>75.66904840823199</v>
       </c>
       <c r="E100">
-        <v>401.69668</v>
+        <v>405.79834</v>
       </c>
       <c r="F100">
-        <v>401.96268</v>
+        <v>406.06434</v>
       </c>
       <c r="G100">
         <v>60.3</v>
@@ -10936,37 +10936,37 @@
         <v>5.02</v>
       </c>
       <c r="M100">
-        <v>94.782799944</v>
+        <v>95.749971372</v>
       </c>
       <c r="N100">
-        <v>-89.76279994400001</v>
+        <v>-90.72997137200001</v>
       </c>
       <c r="O100">
-        <v>-23.78714198516</v>
+        <v>-24.04344241358</v>
       </c>
       <c r="P100">
-        <v>-65.97565795884</v>
+        <v>-66.68652895842001</v>
       </c>
       <c r="Q100">
-        <v>-62.09565795884</v>
+        <v>-62.80652895842001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.55266901652666</v>
+        <v>5.059538033053321</v>
       </c>
       <c r="T100">
-        <v>57.8953583493455</v>
+        <v>115.790716698691</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0140352469096289</v>
+        <v>0.01389347673882457</v>
       </c>
       <c r="W100">
-        <v>0.2324904887787095</v>
+        <v>0.2325239181849852</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10974,91 +10974,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.052963195885392</v>
+        <v>0.05242821410877185</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2807940593336686</v>
-      </c>
-      <c r="C101">
-        <v>-270.095291591768</v>
-      </c>
-      <c r="D101">
-        <v>75.66904840823199</v>
-      </c>
-      <c r="E101">
-        <v>405.79834</v>
-      </c>
-      <c r="F101">
-        <v>406.06434</v>
-      </c>
-      <c r="G101">
-        <v>60.3</v>
-      </c>
-      <c r="H101">
-        <v>409.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.9</v>
-      </c>
-      <c r="K101">
-        <v>3.88</v>
-      </c>
-      <c r="L101">
-        <v>5.02</v>
-      </c>
-      <c r="M101">
-        <v>95.749971372</v>
-      </c>
-      <c r="N101">
-        <v>-90.72997137200001</v>
-      </c>
-      <c r="O101">
-        <v>-24.04344241358</v>
-      </c>
-      <c r="P101">
-        <v>-66.68652895842001</v>
-      </c>
-      <c r="Q101">
-        <v>-62.80652895842001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.059538033053321</v>
-      </c>
-      <c r="T101">
-        <v>115.790716698691</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01389347673882457</v>
-      </c>
-      <c r="W101">
-        <v>0.2325239181849852</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.05242821410877185</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
